--- a/outputs/daily/hr_rankings_2026-10-01.xlsx
+++ b/outputs/daily/hr_rankings_2026-10-01.xlsx
@@ -735,24 +735,24 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>656941</t>
+          <t>621566</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Kyle Schwarber</t>
+          <t>Matt Olson</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
+          <t>ATL</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
           <t>PHI</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>ATL</t>
-        </is>
-      </c>
       <c r="F2" t="inlineStr">
         <is>
           <t>2026-10-02T00:00:00Z</t>
@@ -765,14 +765,26 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Aaron Nola</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>605400</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
       <c r="L2" t="n">
-        <v>57.9</v>
+        <v>59</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -786,26 +798,26 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot</t>
+          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P2" t="n">
-        <v>73.2</v>
+        <v>65.2</v>
       </c>
       <c r="Q2" t="n">
-        <v>41.2</v>
+        <v>47.8</v>
       </c>
       <c r="R2" t="n">
         <v>30.9</v>
       </c>
       <c r="S2" t="n">
-        <v>95.5</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="T2" t="n">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="U2" t="n">
-        <v>8.1</v>
+        <v>25.3</v>
       </c>
       <c r="V2" t="inlineStr">
         <is>
@@ -819,7 +831,7 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
@@ -844,7 +856,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD2" t="inlineStr"/>
@@ -866,32 +878,32 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/23, 0 HR</t>
+          <t>Last 7 games: 4/24, 1 HR</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 9.2% barrel, 31.3 HR allowed</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>lift-pull EV profile; pitcher fly-ball pressure modest</t>
+          <t>EV profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>17.16</t>
+          <t>14.26</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
@@ -901,65 +913,89 @@
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>92.9</t>
+          <t>92.74</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>104.176</t>
+          <t>103.6622</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>0.5152</t>
+          <t>0.4997</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
         <is>
-          <t>0.2756</t>
+          <t>0.2524</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>0.3751</t>
+          <t>0.3537</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
         <is>
-          <t>77.16</t>
+          <t>74.53</t>
         </is>
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>75.35</t>
+          <t>47.33</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>54.35</t>
+          <t>37.44</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>32.62</t>
+          <t>33.27</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>48.3</t>
+          <t>37.4</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>0.2866</t>
-        </is>
-      </c>
-      <c r="BA2" t="inlineStr"/>
-      <c r="BB2" t="inlineStr"/>
-      <c r="BC2" t="inlineStr"/>
-      <c r="BD2" t="inlineStr"/>
-      <c r="BE2" t="inlineStr"/>
-      <c r="BF2" t="inlineStr"/>
+          <t>0.2393</t>
+        </is>
+      </c>
+      <c r="BA2" t="inlineStr">
+        <is>
+          <t>9.24</t>
+        </is>
+      </c>
+      <c r="BB2" t="inlineStr">
+        <is>
+          <t>41.2</t>
+        </is>
+      </c>
+      <c r="BC2" t="inlineStr">
+        <is>
+          <t>88.77</t>
+        </is>
+      </c>
+      <c r="BD2" t="inlineStr">
+        <is>
+          <t>0.4184</t>
+        </is>
+      </c>
+      <c r="BE2" t="inlineStr">
+        <is>
+          <t>0.1745</t>
+        </is>
+      </c>
+      <c r="BF2" t="inlineStr">
+        <is>
+          <t>27.39</t>
+        </is>
+      </c>
       <c r="BG2" t="inlineStr"/>
       <c r="BH2" t="inlineStr"/>
       <c r="BI2" t="inlineStr">
@@ -975,12 +1011,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>621566</t>
+          <t>686948</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Matt Olson</t>
+          <t>Drake Baldwin</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -1005,14 +1041,26 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Aaron Nola</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>605400</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
       <c r="L3" t="n">
-        <v>55.6</v>
+        <v>57.4</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -1026,26 +1074,26 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot</t>
+          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P3" t="n">
-        <v>65.2</v>
+        <v>56.6</v>
       </c>
       <c r="Q3" t="n">
-        <v>41.2</v>
+        <v>47.8</v>
       </c>
       <c r="R3" t="n">
         <v>30.9</v>
       </c>
       <c r="S3" t="n">
-        <v>92.09999999999999</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="T3" t="n">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="U3" t="n">
-        <v>25.3</v>
+        <v>55.3</v>
       </c>
       <c r="V3" t="inlineStr">
         <is>
@@ -1059,7 +1107,7 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -1084,7 +1132,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD3" t="inlineStr"/>
@@ -1101,12 +1149,12 @@
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>11</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>30</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
@@ -1116,90 +1164,114 @@
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/24, 1 HR</t>
+          <t>Contact streak: 11/30 over last 7 games</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 9.2% barrel, 31.3 HR allowed</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>EV profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>14.26</t>
+          <t>12.33</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>52.39</t>
+          <t>50.3</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>92.74</t>
+          <t>91.56</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>103.6622</t>
+          <t>102.2364</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>0.4997</t>
+          <t>0.4975</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
         <is>
-          <t>0.2524</t>
+          <t>0.2206</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>0.3537</t>
+          <t>0.3649</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
         <is>
-          <t>74.53</t>
+          <t>75.3</t>
         </is>
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>47.33</t>
+          <t>56.58</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>37.44</t>
+          <t>32.15</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>33.27</t>
+          <t>25.88</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>37.4</t>
+          <t>23.2</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>0.2393</t>
-        </is>
-      </c>
-      <c r="BA3" t="inlineStr"/>
-      <c r="BB3" t="inlineStr"/>
-      <c r="BC3" t="inlineStr"/>
-      <c r="BD3" t="inlineStr"/>
-      <c r="BE3" t="inlineStr"/>
-      <c r="BF3" t="inlineStr"/>
+          <t>0.181</t>
+        </is>
+      </c>
+      <c r="BA3" t="inlineStr">
+        <is>
+          <t>9.24</t>
+        </is>
+      </c>
+      <c r="BB3" t="inlineStr">
+        <is>
+          <t>41.2</t>
+        </is>
+      </c>
+      <c r="BC3" t="inlineStr">
+        <is>
+          <t>88.77</t>
+        </is>
+      </c>
+      <c r="BD3" t="inlineStr">
+        <is>
+          <t>0.4184</t>
+        </is>
+      </c>
+      <c r="BE3" t="inlineStr">
+        <is>
+          <t>0.1745</t>
+        </is>
+      </c>
+      <c r="BF3" t="inlineStr">
+        <is>
+          <t>27.39</t>
+        </is>
+      </c>
       <c r="BG3" t="inlineStr"/>
       <c r="BH3" t="inlineStr"/>
       <c r="BI3" t="inlineStr">
@@ -1248,11 +1320,23 @@
           <t>2</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Aaron Nola</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>605400</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
       <c r="L4" t="n">
-        <v>55.3</v>
+        <v>56</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
@@ -1273,7 +1357,7 @@
         <v>58.7</v>
       </c>
       <c r="Q4" t="n">
-        <v>41.2</v>
+        <v>47.8</v>
       </c>
       <c r="R4" t="n">
         <v>30.9</v>
@@ -1282,7 +1366,7 @@
         <v>95.5</v>
       </c>
       <c r="T4" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="U4" t="n">
         <v>53.3</v>
@@ -1324,7 +1408,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD4" t="inlineStr"/>
@@ -1361,7 +1445,7 @@
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 9.2% barrel, 31.3 HR allowed</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
@@ -1434,12 +1518,36 @@
           <t>0.2056</t>
         </is>
       </c>
-      <c r="BA4" t="inlineStr"/>
-      <c r="BB4" t="inlineStr"/>
-      <c r="BC4" t="inlineStr"/>
-      <c r="BD4" t="inlineStr"/>
-      <c r="BE4" t="inlineStr"/>
-      <c r="BF4" t="inlineStr"/>
+      <c r="BA4" t="inlineStr">
+        <is>
+          <t>9.24</t>
+        </is>
+      </c>
+      <c r="BB4" t="inlineStr">
+        <is>
+          <t>41.2</t>
+        </is>
+      </c>
+      <c r="BC4" t="inlineStr">
+        <is>
+          <t>88.77</t>
+        </is>
+      </c>
+      <c r="BD4" t="inlineStr">
+        <is>
+          <t>0.4184</t>
+        </is>
+      </c>
+      <c r="BE4" t="inlineStr">
+        <is>
+          <t>0.1745</t>
+        </is>
+      </c>
+      <c r="BF4" t="inlineStr">
+        <is>
+          <t>27.39</t>
+        </is>
+      </c>
       <c r="BG4" t="inlineStr"/>
       <c r="BH4" t="inlineStr"/>
       <c r="BI4" t="inlineStr">
@@ -1455,12 +1563,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>686948</t>
+          <t>671739</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Drake Baldwin</t>
+          <t>Michael Harris</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1485,14 +1593,26 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Aaron Nola</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>605400</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
       <c r="L5" t="n">
-        <v>54</v>
+        <v>52.2</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -1506,26 +1626,26 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot</t>
+          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P5" t="n">
-        <v>56.6</v>
+        <v>45.1</v>
       </c>
       <c r="Q5" t="n">
-        <v>41.2</v>
+        <v>47.8</v>
       </c>
       <c r="R5" t="n">
         <v>30.9</v>
       </c>
       <c r="S5" t="n">
-        <v>90.40000000000001</v>
+        <v>88.7</v>
       </c>
       <c r="T5" t="n">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="U5" t="n">
-        <v>55.3</v>
+        <v>32</v>
       </c>
       <c r="V5" t="inlineStr">
         <is>
@@ -1539,7 +1659,7 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
@@ -1564,7 +1684,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD5" t="inlineStr"/>
@@ -1581,27 +1701,27 @@
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>Contact streak: 11/30 over last 7 games</t>
+          <t>Contact streak: 9/27 over last 7 games</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 9.2% barrel, 31.3 HR allowed</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
@@ -1611,75 +1731,99 @@
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>12.33</t>
+          <t>9.94</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>50.3</t>
+          <t>46.34</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>91.56</t>
+          <t>90.41</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>102.2364</t>
+          <t>103.0958</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>0.4975</t>
+          <t>0.4653</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
-          <t>0.2206</t>
+          <t>0.1816</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>0.3649</t>
+          <t>0.3339</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
         <is>
-          <t>75.3</t>
+          <t>74.72</t>
         </is>
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>56.58</t>
+          <t>47.05</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>32.15</t>
+          <t>35.66</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>25.88</t>
+          <t>22.42</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>23.2</t>
+          <t>24.2</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>0.181</t>
-        </is>
-      </c>
-      <c r="BA5" t="inlineStr"/>
-      <c r="BB5" t="inlineStr"/>
-      <c r="BC5" t="inlineStr"/>
-      <c r="BD5" t="inlineStr"/>
-      <c r="BE5" t="inlineStr"/>
-      <c r="BF5" t="inlineStr"/>
+          <t>0.1859</t>
+        </is>
+      </c>
+      <c r="BA5" t="inlineStr">
+        <is>
+          <t>9.24</t>
+        </is>
+      </c>
+      <c r="BB5" t="inlineStr">
+        <is>
+          <t>41.2</t>
+        </is>
+      </c>
+      <c r="BC5" t="inlineStr">
+        <is>
+          <t>88.77</t>
+        </is>
+      </c>
+      <c r="BD5" t="inlineStr">
+        <is>
+          <t>0.4184</t>
+        </is>
+      </c>
+      <c r="BE5" t="inlineStr">
+        <is>
+          <t>0.1745</t>
+        </is>
+      </c>
+      <c r="BF5" t="inlineStr">
+        <is>
+          <t>27.39</t>
+        </is>
+      </c>
       <c r="BG5" t="inlineStr"/>
       <c r="BH5" t="inlineStr"/>
       <c r="BI5" t="inlineStr">
@@ -1695,12 +1839,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>547180</t>
+          <t>656941</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Bryce Harper</t>
+          <t>Kyle Schwarber</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1725,14 +1869,26 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Ray Kerr</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>678061</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
       <c r="L6" t="n">
-        <v>50.6</v>
+        <v>51.9</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -1750,22 +1906,22 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>49</v>
+        <v>73.2</v>
       </c>
       <c r="Q6" t="n">
-        <v>41.2</v>
+        <v>20</v>
       </c>
       <c r="R6" t="n">
         <v>30.9</v>
       </c>
       <c r="S6" t="n">
-        <v>92.09999999999999</v>
+        <v>95.5</v>
       </c>
       <c r="T6" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="U6" t="n">
-        <v>32.5</v>
+        <v>8.1</v>
       </c>
       <c r="V6" t="inlineStr">
         <is>
@@ -1779,7 +1935,7 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
@@ -1804,7 +1960,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:</t>
+          <t>H:2026/2025 P:2026</t>
         </is>
       </c>
       <c r="AD6" t="inlineStr"/>
@@ -1821,105 +1977,129 @@
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>23</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/28, 1 HR</t>
+          <t>Last 7 games: 4/23, 0 HR</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 5.9% barrel, 2.0 HR allowed</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>lift-pull EV profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>10.9</t>
+          <t>17.16</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>44.21</t>
+          <t>52.39</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>90.39</t>
+          <t>92.9</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>101.6293</t>
+          <t>104.176</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>0.4843</t>
+          <t>0.5152</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
-          <t>0.2142</t>
+          <t>0.2756</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>0.3757</t>
+          <t>0.3751</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
         <is>
-          <t>74.1</t>
+          <t>77.16</t>
         </is>
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>45.01</t>
+          <t>75.35</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>38.47</t>
+          <t>54.35</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>26.82</t>
+          <t>32.62</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>28.4</t>
+          <t>48.3</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>0.219</t>
-        </is>
-      </c>
-      <c r="BA6" t="inlineStr"/>
-      <c r="BB6" t="inlineStr"/>
-      <c r="BC6" t="inlineStr"/>
-      <c r="BD6" t="inlineStr"/>
-      <c r="BE6" t="inlineStr"/>
-      <c r="BF6" t="inlineStr"/>
+          <t>0.2866</t>
+        </is>
+      </c>
+      <c r="BA6" t="inlineStr">
+        <is>
+          <t>5.9</t>
+        </is>
+      </c>
+      <c r="BB6" t="inlineStr">
+        <is>
+          <t>31.4</t>
+        </is>
+      </c>
+      <c r="BC6" t="inlineStr">
+        <is>
+          <t>88.0</t>
+        </is>
+      </c>
+      <c r="BD6" t="inlineStr">
+        <is>
+          <t>0.357</t>
+        </is>
+      </c>
+      <c r="BE6" t="inlineStr">
+        <is>
+          <t>0.119</t>
+        </is>
+      </c>
+      <c r="BF6" t="inlineStr">
+        <is>
+          <t>19.6</t>
+        </is>
+      </c>
       <c r="BG6" t="inlineStr"/>
       <c r="BH6" t="inlineStr"/>
       <c r="BI6" t="inlineStr">
@@ -1935,12 +2115,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>671739</t>
+          <t>663586</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Michael Harris</t>
+          <t>Austin Riley</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1965,14 +2145,26 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Aaron Nola</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>605400</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
       <c r="L7" t="n">
-        <v>48.8</v>
+        <v>47.4</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -1986,26 +2178,26 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot</t>
+          <t>Projected Lineup, Strong Barrel</t>
         </is>
       </c>
       <c r="P7" t="n">
-        <v>45.1</v>
+        <v>53.3</v>
       </c>
       <c r="Q7" t="n">
-        <v>41.2</v>
+        <v>47.8</v>
       </c>
       <c r="R7" t="n">
         <v>30.9</v>
       </c>
       <c r="S7" t="n">
-        <v>88.7</v>
+        <v>47.9</v>
       </c>
       <c r="T7" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="U7" t="n">
-        <v>32</v>
+        <v>48.7</v>
       </c>
       <c r="V7" t="inlineStr">
         <is>
@@ -2019,7 +2211,7 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
@@ -2044,7 +2236,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD7" t="inlineStr"/>
@@ -2061,27 +2253,27 @@
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>Contact streak: 9/27 over last 7 games</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 9.2% barrel, 31.3 HR allowed</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
@@ -2091,75 +2283,99 @@
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>9.94</t>
+          <t>13.24</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>46.34</t>
+          <t>46.07</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>90.41</t>
+          <t>91.6</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>103.0958</t>
+          <t>102.7231</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>0.4653</t>
+          <t>0.4188</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
-          <t>0.1816</t>
+          <t>0.1956</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>0.3339</t>
+          <t>0.3083</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
         <is>
-          <t>74.72</t>
+          <t>75.83</t>
         </is>
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>47.05</t>
+          <t>59.36</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>35.66</t>
+          <t>40.43</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>22.42</t>
+          <t>30.87</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>24.2</t>
+          <t>18.1</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>0.1859</t>
-        </is>
-      </c>
-      <c r="BA7" t="inlineStr"/>
-      <c r="BB7" t="inlineStr"/>
-      <c r="BC7" t="inlineStr"/>
-      <c r="BD7" t="inlineStr"/>
-      <c r="BE7" t="inlineStr"/>
-      <c r="BF7" t="inlineStr"/>
+          <t>0.1519</t>
+        </is>
+      </c>
+      <c r="BA7" t="inlineStr">
+        <is>
+          <t>9.24</t>
+        </is>
+      </c>
+      <c r="BB7" t="inlineStr">
+        <is>
+          <t>41.2</t>
+        </is>
+      </c>
+      <c r="BC7" t="inlineStr">
+        <is>
+          <t>88.77</t>
+        </is>
+      </c>
+      <c r="BD7" t="inlineStr">
+        <is>
+          <t>0.4184</t>
+        </is>
+      </c>
+      <c r="BE7" t="inlineStr">
+        <is>
+          <t>0.1745</t>
+        </is>
+      </c>
+      <c r="BF7" t="inlineStr">
+        <is>
+          <t>27.39</t>
+        </is>
+      </c>
       <c r="BG7" t="inlineStr"/>
       <c r="BH7" t="inlineStr"/>
       <c r="BI7" t="inlineStr">
@@ -2175,24 +2391,24 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>663586</t>
+          <t>547180</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Austin Riley</t>
+          <t>Bryce Harper</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
+          <t>PHI</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
           <t>ATL</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>PHI</t>
-        </is>
-      </c>
       <c r="F8" t="inlineStr">
         <is>
           <t>2026-10-02T00:00:00Z</t>
@@ -2205,14 +2421,26 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Ray Kerr</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>678061</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
       <c r="L8" t="n">
-        <v>46.7</v>
+        <v>44.6</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -2226,26 +2454,26 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel</t>
+          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P8" t="n">
-        <v>53.3</v>
+        <v>49</v>
       </c>
       <c r="Q8" t="n">
-        <v>41.2</v>
+        <v>20</v>
       </c>
       <c r="R8" t="n">
         <v>30.9</v>
       </c>
       <c r="S8" t="n">
-        <v>47.9</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="T8" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="U8" t="n">
-        <v>48.7</v>
+        <v>32.5</v>
       </c>
       <c r="V8" t="inlineStr">
         <is>
@@ -2259,7 +2487,7 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>3</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
@@ -2284,7 +2512,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:</t>
+          <t>H:2026/2025 P:2026</t>
         </is>
       </c>
       <c r="AD8" t="inlineStr"/>
@@ -2301,27 +2529,27 @@
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>28</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Last 7 games: 6/28, 1 HR</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 5.9% barrel, 2.0 HR allowed</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
@@ -2331,75 +2559,99 @@
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>13.24</t>
+          <t>10.9</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>46.07</t>
+          <t>44.21</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>91.6</t>
+          <t>90.39</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>102.7231</t>
+          <t>101.6293</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>0.4188</t>
+          <t>0.4843</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
-          <t>0.1956</t>
+          <t>0.2142</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>0.3083</t>
+          <t>0.3757</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
         <is>
-          <t>75.83</t>
+          <t>74.1</t>
         </is>
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>59.36</t>
+          <t>45.01</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>40.43</t>
+          <t>38.47</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>30.87</t>
+          <t>26.82</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>18.1</t>
+          <t>28.4</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>0.1519</t>
-        </is>
-      </c>
-      <c r="BA8" t="inlineStr"/>
-      <c r="BB8" t="inlineStr"/>
-      <c r="BC8" t="inlineStr"/>
-      <c r="BD8" t="inlineStr"/>
-      <c r="BE8" t="inlineStr"/>
-      <c r="BF8" t="inlineStr"/>
+          <t>0.219</t>
+        </is>
+      </c>
+      <c r="BA8" t="inlineStr">
+        <is>
+          <t>5.9</t>
+        </is>
+      </c>
+      <c r="BB8" t="inlineStr">
+        <is>
+          <t>31.4</t>
+        </is>
+      </c>
+      <c r="BC8" t="inlineStr">
+        <is>
+          <t>88.0</t>
+        </is>
+      </c>
+      <c r="BD8" t="inlineStr">
+        <is>
+          <t>0.357</t>
+        </is>
+      </c>
+      <c r="BE8" t="inlineStr">
+        <is>
+          <t>0.119</t>
+        </is>
+      </c>
+      <c r="BF8" t="inlineStr">
+        <is>
+          <t>19.6</t>
+        </is>
+      </c>
       <c r="BG8" t="inlineStr"/>
       <c r="BH8" t="inlineStr"/>
       <c r="BI8" t="inlineStr">
@@ -2415,24 +2667,24 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>669016</t>
+          <t>573262</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Brandon Marsh</t>
+          <t>Mike Yastrzemski</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
+          <t>ATL</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
           <t>PHI</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>ATL</t>
-        </is>
-      </c>
       <c r="F9" t="inlineStr">
         <is>
           <t>2026-10-02T00:00:00Z</t>
@@ -2445,14 +2697,26 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Aaron Nola</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>605400</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
       <c r="L9" t="n">
-        <v>43.7</v>
+        <v>44.4</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -2466,26 +2730,26 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Projected Lineup, Platoon Edge</t>
         </is>
       </c>
       <c r="P9" t="n">
-        <v>36.1</v>
+        <v>34.7</v>
       </c>
       <c r="Q9" t="n">
-        <v>41.2</v>
+        <v>47.8</v>
       </c>
       <c r="R9" t="n">
         <v>30.9</v>
       </c>
       <c r="S9" t="n">
-        <v>71.7</v>
+        <v>59.8</v>
       </c>
       <c r="T9" t="n">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="U9" t="n">
-        <v>35.6</v>
+        <v>24</v>
       </c>
       <c r="V9" t="inlineStr">
         <is>
@@ -2499,7 +2763,7 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
@@ -2524,7 +2788,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD9" t="inlineStr"/>
@@ -2541,12 +2805,12 @@
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>19</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
@@ -2556,12 +2820,12 @@
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/17, 1 HR</t>
+          <t>Last 7 games: 3/19, 1 HR</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 9.2% barrel, 31.3 HR allowed</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
@@ -2571,75 +2835,99 @@
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>8.12</t>
+          <t>7.31</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>43.74</t>
+          <t>42.88</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>89.77</t>
+          <t>90.52</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>100.0232</t>
+          <t>99.7248</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>0.4103</t>
+          <t>0.3833</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
         <is>
-          <t>0.1564</t>
+          <t>0.1477</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>0.3097</t>
+          <t>0.315</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
         <is>
-          <t>71.54</t>
+          <t>71.24</t>
         </is>
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>15.58</t>
+          <t>8.65</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>38.26</t>
+          <t>43.03</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>26.87</t>
+          <t>30.91</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>15.9</t>
+          <t>13.5</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>0.1525</t>
-        </is>
-      </c>
-      <c r="BA9" t="inlineStr"/>
-      <c r="BB9" t="inlineStr"/>
-      <c r="BC9" t="inlineStr"/>
-      <c r="BD9" t="inlineStr"/>
-      <c r="BE9" t="inlineStr"/>
-      <c r="BF9" t="inlineStr"/>
+          <t>0.1602</t>
+        </is>
+      </c>
+      <c r="BA9" t="inlineStr">
+        <is>
+          <t>9.24</t>
+        </is>
+      </c>
+      <c r="BB9" t="inlineStr">
+        <is>
+          <t>41.2</t>
+        </is>
+      </c>
+      <c r="BC9" t="inlineStr">
+        <is>
+          <t>88.77</t>
+        </is>
+      </c>
+      <c r="BD9" t="inlineStr">
+        <is>
+          <t>0.4184</t>
+        </is>
+      </c>
+      <c r="BE9" t="inlineStr">
+        <is>
+          <t>0.1745</t>
+        </is>
+      </c>
+      <c r="BF9" t="inlineStr">
+        <is>
+          <t>27.39</t>
+        </is>
+      </c>
       <c r="BG9" t="inlineStr"/>
       <c r="BH9" t="inlineStr"/>
       <c r="BI9" t="inlineStr">
@@ -2655,12 +2943,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>681082</t>
+          <t>664761</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Bryson Stott</t>
+          <t>Alec Bohm</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -2685,14 +2973,26 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>Ray Kerr</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>678061</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
       <c r="L10" t="n">
-        <v>42.9</v>
+        <v>39.3</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
@@ -2706,26 +3006,26 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot</t>
+          <t>Projected Lineup, Platoon Edge</t>
         </is>
       </c>
       <c r="P10" t="n">
-        <v>25.2</v>
+        <v>32.7</v>
       </c>
       <c r="Q10" t="n">
-        <v>41.2</v>
+        <v>20</v>
       </c>
       <c r="R10" t="n">
         <v>30.9</v>
       </c>
       <c r="S10" t="n">
-        <v>90.40000000000001</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="T10" t="n">
-        <v>60</v>
+        <v>78</v>
       </c>
       <c r="U10" t="n">
-        <v>40.7</v>
+        <v>10.8</v>
       </c>
       <c r="V10" t="inlineStr">
         <is>
@@ -2739,7 +3039,7 @@
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr">
@@ -2764,7 +3064,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:</t>
+          <t>H:2026/2025 P:2026</t>
         </is>
       </c>
       <c r="AD10" t="inlineStr"/>
@@ -2781,12 +3081,12 @@
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
@@ -2796,12 +3096,12 @@
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>Contact streak: 9/23 over last 7 games</t>
+          <t>Last 7 games: 5/26, 0 HR</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 5.9% barrel, 2.0 HR allowed</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
@@ -2811,75 +3111,99 @@
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>5.66</t>
+          <t>6.06</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>35.24</t>
+          <t>44.58</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>88.86</t>
+          <t>90.66</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>98.4048</t>
+          <t>100.426</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>0.3993</t>
+          <t>0.4123</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
         <is>
-          <t>0.1383</t>
+          <t>0.1446</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>0.3249</t>
+          <t>0.3261</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
         <is>
-          <t>69.72</t>
+          <t>71.28</t>
         </is>
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>6.75</t>
+          <t>15.26</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>34.17</t>
+          <t>28.28</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>27.59</t>
+          <t>22.44</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>10.9</t>
+          <t>13.8</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>0.1417</t>
-        </is>
-      </c>
-      <c r="BA10" t="inlineStr"/>
-      <c r="BB10" t="inlineStr"/>
-      <c r="BC10" t="inlineStr"/>
-      <c r="BD10" t="inlineStr"/>
-      <c r="BE10" t="inlineStr"/>
-      <c r="BF10" t="inlineStr"/>
+          <t>0.1304</t>
+        </is>
+      </c>
+      <c r="BA10" t="inlineStr">
+        <is>
+          <t>5.9</t>
+        </is>
+      </c>
+      <c r="BB10" t="inlineStr">
+        <is>
+          <t>31.4</t>
+        </is>
+      </c>
+      <c r="BC10" t="inlineStr">
+        <is>
+          <t>88.0</t>
+        </is>
+      </c>
+      <c r="BD10" t="inlineStr">
+        <is>
+          <t>0.357</t>
+        </is>
+      </c>
+      <c r="BE10" t="inlineStr">
+        <is>
+          <t>0.119</t>
+        </is>
+      </c>
+      <c r="BF10" t="inlineStr">
+        <is>
+          <t>19.6</t>
+        </is>
+      </c>
       <c r="BG10" t="inlineStr"/>
       <c r="BH10" t="inlineStr"/>
       <c r="BI10" t="inlineStr">
@@ -2895,12 +3219,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>664761</t>
+          <t>607208</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Alec Bohm</t>
+          <t>Trea Turner</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2925,14 +3249,26 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>Ray Kerr</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>678061</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
       <c r="L11" t="n">
-        <v>42.7</v>
+        <v>38.7</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -2946,26 +3282,26 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P11" t="n">
-        <v>32.7</v>
+        <v>26.4</v>
       </c>
       <c r="Q11" t="n">
-        <v>41.2</v>
+        <v>20</v>
       </c>
       <c r="R11" t="n">
         <v>30.9</v>
       </c>
       <c r="S11" t="n">
-        <v>81.90000000000001</v>
+        <v>88.7</v>
       </c>
       <c r="T11" t="n">
-        <v>60</v>
+        <v>78</v>
       </c>
       <c r="U11" t="n">
-        <v>10.8</v>
+        <v>22</v>
       </c>
       <c r="V11" t="inlineStr">
         <is>
@@ -2979,7 +3315,7 @@
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr">
@@ -3004,7 +3340,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:</t>
+          <t>H:2026/2025 P:2026</t>
         </is>
       </c>
       <c r="AD11" t="inlineStr"/>
@@ -3021,12 +3357,12 @@
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>30</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
@@ -3036,12 +3372,12 @@
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/26, 0 HR</t>
+          <t>Last 7 games: 8/30, 0 HR</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 5.9% barrel, 2.0 HR allowed</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
@@ -3051,75 +3387,99 @@
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>6.06</t>
+          <t>5.94</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>44.58</t>
+          <t>40.14</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>90.66</t>
+          <t>88.74</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>100.426</t>
+          <t>99.2936</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>0.4123</t>
+          <t>0.3771</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
         <is>
-          <t>0.1446</t>
+          <t>0.1267</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>0.3261</t>
+          <t>0.3014</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
         <is>
-          <t>71.28</t>
+          <t>71.45</t>
         </is>
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>15.26</t>
+          <t>18.58</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>28.28</t>
+          <t>35.17</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>22.44</t>
+          <t>24.64</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>13.8</t>
+          <t>17.8</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>0.1304</t>
-        </is>
-      </c>
-      <c r="BA11" t="inlineStr"/>
-      <c r="BB11" t="inlineStr"/>
-      <c r="BC11" t="inlineStr"/>
-      <c r="BD11" t="inlineStr"/>
-      <c r="BE11" t="inlineStr"/>
-      <c r="BF11" t="inlineStr"/>
+          <t>0.1411</t>
+        </is>
+      </c>
+      <c r="BA11" t="inlineStr">
+        <is>
+          <t>5.9</t>
+        </is>
+      </c>
+      <c r="BB11" t="inlineStr">
+        <is>
+          <t>31.4</t>
+        </is>
+      </c>
+      <c r="BC11" t="inlineStr">
+        <is>
+          <t>88.0</t>
+        </is>
+      </c>
+      <c r="BD11" t="inlineStr">
+        <is>
+          <t>0.357</t>
+        </is>
+      </c>
+      <c r="BE11" t="inlineStr">
+        <is>
+          <t>0.119</t>
+        </is>
+      </c>
+      <c r="BF11" t="inlineStr">
+        <is>
+          <t>19.6</t>
+        </is>
+      </c>
       <c r="BG11" t="inlineStr"/>
       <c r="BH11" t="inlineStr"/>
       <c r="BI11" t="inlineStr">
@@ -3135,12 +3495,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>607208</t>
+          <t>624641</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Trea Turner</t>
+          <t>Edmundo Sosa</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -3165,14 +3525,26 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>Ray Kerr</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>678061</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
       <c r="L12" t="n">
-        <v>42.2</v>
+        <v>38.4</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
@@ -3186,26 +3558,26 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot</t>
+          <t>Projected Lineup, Platoon Edge, Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P12" t="n">
-        <v>26.4</v>
+        <v>30.1</v>
       </c>
       <c r="Q12" t="n">
-        <v>41.2</v>
+        <v>20</v>
       </c>
       <c r="R12" t="n">
         <v>30.9</v>
       </c>
       <c r="S12" t="n">
-        <v>88.7</v>
+        <v>59.8</v>
       </c>
       <c r="T12" t="n">
-        <v>60</v>
+        <v>78</v>
       </c>
       <c r="U12" t="n">
-        <v>22</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="V12" t="inlineStr">
         <is>
@@ -3219,7 +3591,7 @@
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>7</t>
         </is>
       </c>
       <c r="Y12" t="inlineStr">
@@ -3244,7 +3616,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:</t>
+          <t>H:2026/2025 P:2026</t>
         </is>
       </c>
       <c r="AD12" t="inlineStr"/>
@@ -3261,27 +3633,27 @@
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>17</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>Last 7 games: 8/30, 0 HR</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 5.9% barrel, 2.0 HR allowed</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
@@ -3291,75 +3663,99 @@
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>5.94</t>
+          <t>6.93</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>40.14</t>
+          <t>38.84</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>88.74</t>
+          <t>87.77</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>99.2936</t>
+          <t>99.9033</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>0.3771</t>
+          <t>0.4281</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
         <is>
-          <t>0.1267</t>
+          <t>0.1614</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>0.3014</t>
+          <t>0.3166</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
         <is>
-          <t>71.45</t>
+          <t>72.44</t>
         </is>
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>18.58</t>
+          <t>27.29</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>35.17</t>
+          <t>41.31</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>24.64</t>
+          <t>21.78</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>17.8</t>
+          <t>9.6</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>0.1411</t>
-        </is>
-      </c>
-      <c r="BA12" t="inlineStr"/>
-      <c r="BB12" t="inlineStr"/>
-      <c r="BC12" t="inlineStr"/>
-      <c r="BD12" t="inlineStr"/>
-      <c r="BE12" t="inlineStr"/>
-      <c r="BF12" t="inlineStr"/>
+          <t>0.1853</t>
+        </is>
+      </c>
+      <c r="BA12" t="inlineStr">
+        <is>
+          <t>5.9</t>
+        </is>
+      </c>
+      <c r="BB12" t="inlineStr">
+        <is>
+          <t>31.4</t>
+        </is>
+      </c>
+      <c r="BC12" t="inlineStr">
+        <is>
+          <t>88.0</t>
+        </is>
+      </c>
+      <c r="BD12" t="inlineStr">
+        <is>
+          <t>0.357</t>
+        </is>
+      </c>
+      <c r="BE12" t="inlineStr">
+        <is>
+          <t>0.119</t>
+        </is>
+      </c>
+      <c r="BF12" t="inlineStr">
+        <is>
+          <t>19.6</t>
+        </is>
+      </c>
       <c r="BG12" t="inlineStr"/>
       <c r="BH12" t="inlineStr"/>
       <c r="BI12" t="inlineStr">
@@ -3375,24 +3771,24 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>624641</t>
+          <t>643289</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Edmundo Sosa</t>
+          <t>Mauricio Dubon</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
+          <t>ATL</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
           <t>PHI</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>ATL</t>
-        </is>
-      </c>
       <c r="F13" t="inlineStr">
         <is>
           <t>2026-10-02T00:00:00Z</t>
@@ -3405,14 +3801,26 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>Aaron Nola</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>605400</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
       <c r="L13" t="n">
-        <v>41.8</v>
+        <v>38</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
@@ -3426,26 +3834,26 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>Projected Lineup, Hot Hitter/Streak</t>
+          <t>Projected Lineup</t>
         </is>
       </c>
       <c r="P13" t="n">
-        <v>30.1</v>
+        <v>10.2</v>
       </c>
       <c r="Q13" t="n">
-        <v>41.2</v>
+        <v>47.8</v>
       </c>
       <c r="R13" t="n">
         <v>30.9</v>
       </c>
       <c r="S13" t="n">
-        <v>59.8</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="T13" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="U13" t="n">
-        <v>71.59999999999999</v>
+        <v>50.3</v>
       </c>
       <c r="V13" t="inlineStr">
         <is>
@@ -3459,7 +3867,7 @@
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr">
@@ -3484,7 +3892,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD13" t="inlineStr"/>
@@ -3501,27 +3909,27 @@
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Contact streak: 9/27 over last 7 games</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 9.2% barrel, 31.3 HR allowed</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
@@ -3531,75 +3939,99 @@
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>6.93</t>
+          <t>3.16</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>38.84</t>
+          <t>28.47</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>87.77</t>
+          <t>85.9</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>99.9033</t>
+          <t>96.2638</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>0.4281</t>
+          <t>0.3618</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
         <is>
-          <t>0.1614</t>
+          <t>0.1008</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>0.3166</t>
+          <t>0.2962</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
         <is>
-          <t>72.44</t>
+          <t>68.87</t>
         </is>
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>27.29</t>
+          <t>4.1</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>41.31</t>
+          <t>31.89</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>21.78</t>
+          <t>25.86</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>9.6</t>
+          <t>10.5</t>
         </is>
       </c>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>0.1853</t>
-        </is>
-      </c>
-      <c r="BA13" t="inlineStr"/>
-      <c r="BB13" t="inlineStr"/>
-      <c r="BC13" t="inlineStr"/>
-      <c r="BD13" t="inlineStr"/>
-      <c r="BE13" t="inlineStr"/>
-      <c r="BF13" t="inlineStr"/>
+          <t>0.1203</t>
+        </is>
+      </c>
+      <c r="BA13" t="inlineStr">
+        <is>
+          <t>9.24</t>
+        </is>
+      </c>
+      <c r="BB13" t="inlineStr">
+        <is>
+          <t>41.2</t>
+        </is>
+      </c>
+      <c r="BC13" t="inlineStr">
+        <is>
+          <t>88.77</t>
+        </is>
+      </c>
+      <c r="BD13" t="inlineStr">
+        <is>
+          <t>0.4184</t>
+        </is>
+      </c>
+      <c r="BE13" t="inlineStr">
+        <is>
+          <t>0.1745</t>
+        </is>
+      </c>
+      <c r="BF13" t="inlineStr">
+        <is>
+          <t>27.39</t>
+        </is>
+      </c>
       <c r="BG13" t="inlineStr"/>
       <c r="BH13" t="inlineStr"/>
       <c r="BI13" t="inlineStr">
@@ -3615,12 +4047,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>573262</t>
+          <t>645277</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Mike Yastrzemski</t>
+          <t>Ozzie Albies</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -3645,14 +4077,26 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>Aaron Nola</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>605400</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
       <c r="L14" t="n">
-        <v>41</v>
+        <v>37.8</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
@@ -3666,26 +4110,26 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Projected Lineup, Platoon Edge</t>
         </is>
       </c>
       <c r="P14" t="n">
-        <v>34.7</v>
+        <v>15.3</v>
       </c>
       <c r="Q14" t="n">
-        <v>41.2</v>
+        <v>47.3</v>
       </c>
       <c r="R14" t="n">
         <v>30.9</v>
       </c>
       <c r="S14" t="n">
-        <v>59.8</v>
+        <v>71.7</v>
       </c>
       <c r="T14" t="n">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="U14" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="V14" t="inlineStr">
         <is>
@@ -3699,7 +4143,7 @@
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="Y14" t="inlineStr">
@@ -3724,7 +4168,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD14" t="inlineStr"/>
@@ -3746,22 +4190,22 @@
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>Last 7 games: 3/19, 1 HR</t>
+          <t>Last 7 games: 3/25, 0 HR</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>switch hitter; pitcher baseline 9.2% barrel, 31.3 HR allowed</t>
         </is>
       </c>
       <c r="AM14" t="inlineStr">
@@ -3771,75 +4215,99 @@
       </c>
       <c r="AN14" t="inlineStr">
         <is>
-          <t>7.31</t>
+          <t>4.13</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>42.88</t>
+          <t>28.6</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>90.52</t>
+          <t>87.22</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>99.7248</t>
+          <t>96.687</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>0.3833</t>
+          <t>0.346</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
         <is>
-          <t>0.1477</t>
+          <t>0.1184</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>0.315</t>
+          <t>0.2808</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
         <is>
-          <t>71.24</t>
+          <t>68.86</t>
         </is>
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>8.65</t>
+          <t>5.67</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>43.03</t>
+          <t>46.7</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>30.91</t>
+          <t>31.48</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>13.5</t>
+          <t>20.2</t>
         </is>
       </c>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>0.1602</t>
-        </is>
-      </c>
-      <c r="BA14" t="inlineStr"/>
-      <c r="BB14" t="inlineStr"/>
-      <c r="BC14" t="inlineStr"/>
-      <c r="BD14" t="inlineStr"/>
-      <c r="BE14" t="inlineStr"/>
-      <c r="BF14" t="inlineStr"/>
+          <t>0.146</t>
+        </is>
+      </c>
+      <c r="BA14" t="inlineStr">
+        <is>
+          <t>9.24</t>
+        </is>
+      </c>
+      <c r="BB14" t="inlineStr">
+        <is>
+          <t>41.2</t>
+        </is>
+      </c>
+      <c r="BC14" t="inlineStr">
+        <is>
+          <t>88.77</t>
+        </is>
+      </c>
+      <c r="BD14" t="inlineStr">
+        <is>
+          <t>0.4184</t>
+        </is>
+      </c>
+      <c r="BE14" t="inlineStr">
+        <is>
+          <t>0.1745</t>
+        </is>
+      </c>
+      <c r="BF14" t="inlineStr">
+        <is>
+          <t>27.39</t>
+        </is>
+      </c>
       <c r="BG14" t="inlineStr"/>
       <c r="BH14" t="inlineStr"/>
       <c r="BI14" t="inlineStr">
@@ -3855,24 +4323,24 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>643289</t>
+          <t>669016</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Mauricio Dubon</t>
+          <t>Brandon Marsh</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
+          <t>PHI</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
           <t>ATL</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>PHI</t>
-        </is>
-      </c>
       <c r="F15" t="inlineStr">
         <is>
           <t>2026-10-02T00:00:00Z</t>
@@ -3885,14 +4353,26 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>Ray Kerr</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>678061</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
       <c r="L15" t="n">
-        <v>37.3</v>
+        <v>37.7</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
@@ -3910,22 +4390,22 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>10.2</v>
+        <v>36.1</v>
       </c>
       <c r="Q15" t="n">
-        <v>41.2</v>
+        <v>20</v>
       </c>
       <c r="R15" t="n">
         <v>30.9</v>
       </c>
       <c r="S15" t="n">
-        <v>81.90000000000001</v>
+        <v>71.7</v>
       </c>
       <c r="T15" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="U15" t="n">
-        <v>50.3</v>
+        <v>35.6</v>
       </c>
       <c r="V15" t="inlineStr">
         <is>
@@ -3939,7 +4419,7 @@
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="Y15" t="inlineStr">
@@ -3964,7 +4444,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:</t>
+          <t>H:2026/2025 P:2026</t>
         </is>
       </c>
       <c r="AD15" t="inlineStr"/>
@@ -3981,12 +4461,12 @@
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>17</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
@@ -3996,12 +4476,12 @@
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>Contact streak: 9/27 over last 7 games</t>
+          <t>Last 7 games: 4/17, 1 HR</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 5.9% barrel, 2.0 HR allowed</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
@@ -4011,75 +4491,99 @@
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>3.16</t>
+          <t>8.12</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>28.47</t>
+          <t>43.74</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>85.9</t>
+          <t>89.77</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>96.2638</t>
+          <t>100.0232</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>0.3618</t>
+          <t>0.4103</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
         <is>
-          <t>0.1008</t>
+          <t>0.1564</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>0.2962</t>
+          <t>0.3097</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
         <is>
-          <t>68.87</t>
+          <t>71.54</t>
         </is>
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>4.1</t>
+          <t>15.58</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>31.89</t>
+          <t>38.26</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>25.86</t>
+          <t>26.87</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>10.5</t>
+          <t>15.9</t>
         </is>
       </c>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>0.1203</t>
-        </is>
-      </c>
-      <c r="BA15" t="inlineStr"/>
-      <c r="BB15" t="inlineStr"/>
-      <c r="BC15" t="inlineStr"/>
-      <c r="BD15" t="inlineStr"/>
-      <c r="BE15" t="inlineStr"/>
-      <c r="BF15" t="inlineStr"/>
+          <t>0.1525</t>
+        </is>
+      </c>
+      <c r="BA15" t="inlineStr">
+        <is>
+          <t>5.9</t>
+        </is>
+      </c>
+      <c r="BB15" t="inlineStr">
+        <is>
+          <t>31.4</t>
+        </is>
+      </c>
+      <c r="BC15" t="inlineStr">
+        <is>
+          <t>88.0</t>
+        </is>
+      </c>
+      <c r="BD15" t="inlineStr">
+        <is>
+          <t>0.357</t>
+        </is>
+      </c>
+      <c r="BE15" t="inlineStr">
+        <is>
+          <t>0.119</t>
+        </is>
+      </c>
+      <c r="BF15" t="inlineStr">
+        <is>
+          <t>19.6</t>
+        </is>
+      </c>
       <c r="BG15" t="inlineStr"/>
       <c r="BH15" t="inlineStr"/>
       <c r="BI15" t="inlineStr">
@@ -4128,11 +4632,23 @@
           <t>9</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>Aaron Nola</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>605400</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
       <c r="L16" t="n">
-        <v>37</v>
+        <v>37.6</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
@@ -4153,7 +4669,7 @@
         <v>34</v>
       </c>
       <c r="Q16" t="n">
-        <v>41.2</v>
+        <v>47.8</v>
       </c>
       <c r="R16" t="n">
         <v>30.9</v>
@@ -4162,7 +4678,7 @@
         <v>40.2</v>
       </c>
       <c r="T16" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="U16" t="n">
         <v>3.4</v>
@@ -4204,7 +4720,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD16" t="inlineStr"/>
@@ -4241,7 +4757,7 @@
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 9.2% barrel, 31.3 HR allowed</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
@@ -4314,12 +4830,36 @@
           <t>0.1456</t>
         </is>
       </c>
-      <c r="BA16" t="inlineStr"/>
-      <c r="BB16" t="inlineStr"/>
-      <c r="BC16" t="inlineStr"/>
-      <c r="BD16" t="inlineStr"/>
-      <c r="BE16" t="inlineStr"/>
-      <c r="BF16" t="inlineStr"/>
+      <c r="BA16" t="inlineStr">
+        <is>
+          <t>9.24</t>
+        </is>
+      </c>
+      <c r="BB16" t="inlineStr">
+        <is>
+          <t>41.2</t>
+        </is>
+      </c>
+      <c r="BC16" t="inlineStr">
+        <is>
+          <t>88.77</t>
+        </is>
+      </c>
+      <c r="BD16" t="inlineStr">
+        <is>
+          <t>0.4184</t>
+        </is>
+      </c>
+      <c r="BE16" t="inlineStr">
+        <is>
+          <t>0.1745</t>
+        </is>
+      </c>
+      <c r="BF16" t="inlineStr">
+        <is>
+          <t>27.39</t>
+        </is>
+      </c>
       <c r="BG16" t="inlineStr"/>
       <c r="BH16" t="inlineStr"/>
       <c r="BI16" t="inlineStr">
@@ -4335,12 +4875,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>592663</t>
+          <t>681082</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>J.T. Realmuto</t>
+          <t>Bryson Stott</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -4365,14 +4905,26 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>Ray Kerr</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>678061</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
       <c r="L17" t="n">
-        <v>36.1</v>
+        <v>36.9</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
@@ -4386,26 +4938,26 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Projected Lineup, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P17" t="n">
-        <v>32</v>
+        <v>25.2</v>
       </c>
       <c r="Q17" t="n">
-        <v>41.2</v>
+        <v>20</v>
       </c>
       <c r="R17" t="n">
         <v>30.9</v>
       </c>
       <c r="S17" t="n">
-        <v>40.2</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="T17" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>40.7</v>
       </c>
       <c r="V17" t="inlineStr">
         <is>
@@ -4419,7 +4971,7 @@
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>4</t>
         </is>
       </c>
       <c r="Y17" t="inlineStr">
@@ -4444,7 +4996,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:</t>
+          <t>H:2026/2025 P:2026</t>
         </is>
       </c>
       <c r="AD17" t="inlineStr"/>
@@ -4461,12 +5013,12 @@
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>23</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
@@ -4476,12 +5028,12 @@
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>Last 7 games: 1/21, 0 HR</t>
+          <t>Contact streak: 9/23 over last 7 games</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 5.9% barrel, 2.0 HR allowed</t>
         </is>
       </c>
       <c r="AM17" t="inlineStr">
@@ -4491,75 +5043,99 @@
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>6.63</t>
+          <t>5.66</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>41.65</t>
+          <t>35.24</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>89.65</t>
+          <t>88.86</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>100.1126</t>
+          <t>98.4048</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>0.3942</t>
+          <t>0.3993</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
         <is>
-          <t>0.144</t>
+          <t>0.1383</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>0.3167</t>
+          <t>0.3249</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
         <is>
-          <t>72.77</t>
+          <t>69.72</t>
         </is>
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>30.54</t>
+          <t>6.75</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>41.39</t>
+          <t>34.17</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>25.94</t>
+          <t>27.59</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>11.3</t>
+          <t>10.9</t>
         </is>
       </c>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>0.1263</t>
-        </is>
-      </c>
-      <c r="BA17" t="inlineStr"/>
-      <c r="BB17" t="inlineStr"/>
-      <c r="BC17" t="inlineStr"/>
-      <c r="BD17" t="inlineStr"/>
-      <c r="BE17" t="inlineStr"/>
-      <c r="BF17" t="inlineStr"/>
+          <t>0.1417</t>
+        </is>
+      </c>
+      <c r="BA17" t="inlineStr">
+        <is>
+          <t>5.9</t>
+        </is>
+      </c>
+      <c r="BB17" t="inlineStr">
+        <is>
+          <t>31.4</t>
+        </is>
+      </c>
+      <c r="BC17" t="inlineStr">
+        <is>
+          <t>88.0</t>
+        </is>
+      </c>
+      <c r="BD17" t="inlineStr">
+        <is>
+          <t>0.357</t>
+        </is>
+      </c>
+      <c r="BE17" t="inlineStr">
+        <is>
+          <t>0.119</t>
+        </is>
+      </c>
+      <c r="BF17" t="inlineStr">
+        <is>
+          <t>19.6</t>
+        </is>
+      </c>
       <c r="BG17" t="inlineStr"/>
       <c r="BH17" t="inlineStr"/>
       <c r="BI17" t="inlineStr">
@@ -4575,24 +5151,24 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>645277</t>
+          <t>592663</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Ozzie Albies</t>
+          <t>J.T. Realmuto</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
+          <t>PHI</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
           <t>ATL</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>PHI</t>
-        </is>
-      </c>
       <c r="F18" t="inlineStr">
         <is>
           <t>2026-10-02T00:00:00Z</t>
@@ -4605,14 +5181,26 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>Ray Kerr</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>678061</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
       <c r="L18" t="n">
-        <v>36.1</v>
+        <v>32.7</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
@@ -4630,19 +5218,19 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>15.3</v>
+        <v>32</v>
       </c>
       <c r="Q18" t="n">
-        <v>40.2</v>
+        <v>20</v>
       </c>
       <c r="R18" t="n">
         <v>30.9</v>
       </c>
       <c r="S18" t="n">
-        <v>71.7</v>
+        <v>40.2</v>
       </c>
       <c r="T18" t="n">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="U18" t="n">
         <v>0</v>
@@ -4659,7 +5247,7 @@
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>9</t>
         </is>
       </c>
       <c r="Y18" t="inlineStr">
@@ -4684,7 +5272,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:</t>
+          <t>H:2026/2025 P:2026</t>
         </is>
       </c>
       <c r="AD18" t="inlineStr"/>
@@ -4701,12 +5289,12 @@
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
@@ -4716,12 +5304,12 @@
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>Last 7 games: 3/25, 0 HR</t>
+          <t>Last 7 games: 1/21, 0 HR</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 5.9% barrel, 2.0 HR allowed</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
@@ -4731,75 +5319,99 @@
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>4.13</t>
+          <t>6.63</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>28.6</t>
+          <t>41.65</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>87.22</t>
+          <t>89.65</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>96.687</t>
+          <t>100.1126</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>0.346</t>
+          <t>0.3942</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
         <is>
-          <t>0.1184</t>
+          <t>0.144</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>0.2808</t>
+          <t>0.3167</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
         <is>
-          <t>68.86</t>
+          <t>72.77</t>
         </is>
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>5.67</t>
+          <t>30.54</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>46.7</t>
+          <t>41.39</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>31.48</t>
+          <t>25.94</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>20.2</t>
+          <t>11.3</t>
         </is>
       </c>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>0.146</t>
-        </is>
-      </c>
-      <c r="BA18" t="inlineStr"/>
-      <c r="BB18" t="inlineStr"/>
-      <c r="BC18" t="inlineStr"/>
-      <c r="BD18" t="inlineStr"/>
-      <c r="BE18" t="inlineStr"/>
-      <c r="BF18" t="inlineStr"/>
+          <t>0.1263</t>
+        </is>
+      </c>
+      <c r="BA18" t="inlineStr">
+        <is>
+          <t>5.9</t>
+        </is>
+      </c>
+      <c r="BB18" t="inlineStr">
+        <is>
+          <t>31.4</t>
+        </is>
+      </c>
+      <c r="BC18" t="inlineStr">
+        <is>
+          <t>88.0</t>
+        </is>
+      </c>
+      <c r="BD18" t="inlineStr">
+        <is>
+          <t>0.357</t>
+        </is>
+      </c>
+      <c r="BE18" t="inlineStr">
+        <is>
+          <t>0.119</t>
+        </is>
+      </c>
+      <c r="BF18" t="inlineStr">
+        <is>
+          <t>19.6</t>
+        </is>
+      </c>
       <c r="BG18" t="inlineStr"/>
       <c r="BH18" t="inlineStr"/>
       <c r="BI18" t="inlineStr">
@@ -4848,11 +5460,23 @@
           <t>8</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>Ray Kerr</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>678061</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
       <c r="L19" t="n">
-        <v>31.1</v>
+        <v>25.1</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
@@ -4873,7 +5497,7 @@
         <v>10.9</v>
       </c>
       <c r="Q19" t="n">
-        <v>41.2</v>
+        <v>20</v>
       </c>
       <c r="R19" t="n">
         <v>30.9</v>
@@ -4882,7 +5506,7 @@
         <v>47.9</v>
       </c>
       <c r="T19" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="U19" t="n">
         <v>17.7</v>
@@ -4924,7 +5548,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>H:2026 P:</t>
+          <t>H:2026 P:2026</t>
         </is>
       </c>
       <c r="AD19" t="inlineStr"/>
@@ -4961,7 +5585,7 @@
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 5.9% barrel, 2.0 HR allowed</t>
         </is>
       </c>
       <c r="AM19" t="inlineStr">
@@ -5034,12 +5658,36 @@
           <t>0.089</t>
         </is>
       </c>
-      <c r="BA19" t="inlineStr"/>
-      <c r="BB19" t="inlineStr"/>
-      <c r="BC19" t="inlineStr"/>
-      <c r="BD19" t="inlineStr"/>
-      <c r="BE19" t="inlineStr"/>
-      <c r="BF19" t="inlineStr"/>
+      <c r="BA19" t="inlineStr">
+        <is>
+          <t>5.9</t>
+        </is>
+      </c>
+      <c r="BB19" t="inlineStr">
+        <is>
+          <t>31.4</t>
+        </is>
+      </c>
+      <c r="BC19" t="inlineStr">
+        <is>
+          <t>88.0</t>
+        </is>
+      </c>
+      <c r="BD19" t="inlineStr">
+        <is>
+          <t>0.357</t>
+        </is>
+      </c>
+      <c r="BE19" t="inlineStr">
+        <is>
+          <t>0.119</t>
+        </is>
+      </c>
+      <c r="BF19" t="inlineStr">
+        <is>
+          <t>19.6</t>
+        </is>
+      </c>
       <c r="BG19" t="inlineStr"/>
       <c r="BH19" t="inlineStr"/>
       <c r="BI19" t="inlineStr">
@@ -5381,24 +6029,24 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>656941</t>
+          <t>621566</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Kyle Schwarber</t>
+          <t>Matt Olson</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
+          <t>ATL</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
           <t>PHI</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>ATL</t>
-        </is>
-      </c>
       <c r="F2" t="inlineStr">
         <is>
           <t>2026-10-02T00:00:00Z</t>
@@ -5411,14 +6059,26 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Aaron Nola</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>605400</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
       <c r="L2" t="n">
-        <v>57.9</v>
+        <v>59</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -5432,26 +6092,26 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot</t>
+          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P2" t="n">
-        <v>73.2</v>
+        <v>65.2</v>
       </c>
       <c r="Q2" t="n">
-        <v>41.2</v>
+        <v>47.8</v>
       </c>
       <c r="R2" t="n">
         <v>30.9</v>
       </c>
       <c r="S2" t="n">
-        <v>95.5</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="T2" t="n">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="U2" t="n">
-        <v>8.1</v>
+        <v>25.3</v>
       </c>
       <c r="V2" t="inlineStr">
         <is>
@@ -5465,7 +6125,7 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
@@ -5490,7 +6150,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD2" t="inlineStr"/>
@@ -5512,32 +6172,32 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/23, 0 HR</t>
+          <t>Last 7 games: 4/24, 1 HR</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 9.2% barrel, 31.3 HR allowed</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>lift-pull EV profile; pitcher fly-ball pressure modest</t>
+          <t>EV profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>17.16</t>
+          <t>14.26</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
@@ -5547,65 +6207,89 @@
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>92.9</t>
+          <t>92.74</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>104.176</t>
+          <t>103.6622</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>0.5152</t>
+          <t>0.4997</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
         <is>
-          <t>0.2756</t>
+          <t>0.2524</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>0.3751</t>
+          <t>0.3537</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
         <is>
-          <t>77.16</t>
+          <t>74.53</t>
         </is>
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>75.35</t>
+          <t>47.33</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>54.35</t>
+          <t>37.44</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>32.62</t>
+          <t>33.27</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>48.3</t>
+          <t>37.4</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>0.2866</t>
-        </is>
-      </c>
-      <c r="BA2" t="inlineStr"/>
-      <c r="BB2" t="inlineStr"/>
-      <c r="BC2" t="inlineStr"/>
-      <c r="BD2" t="inlineStr"/>
-      <c r="BE2" t="inlineStr"/>
-      <c r="BF2" t="inlineStr"/>
+          <t>0.2393</t>
+        </is>
+      </c>
+      <c r="BA2" t="inlineStr">
+        <is>
+          <t>9.24</t>
+        </is>
+      </c>
+      <c r="BB2" t="inlineStr">
+        <is>
+          <t>41.2</t>
+        </is>
+      </c>
+      <c r="BC2" t="inlineStr">
+        <is>
+          <t>88.77</t>
+        </is>
+      </c>
+      <c r="BD2" t="inlineStr">
+        <is>
+          <t>0.4184</t>
+        </is>
+      </c>
+      <c r="BE2" t="inlineStr">
+        <is>
+          <t>0.1745</t>
+        </is>
+      </c>
+      <c r="BF2" t="inlineStr">
+        <is>
+          <t>27.39</t>
+        </is>
+      </c>
       <c r="BG2" t="inlineStr"/>
       <c r="BH2" t="inlineStr"/>
       <c r="BI2" t="inlineStr">
@@ -5621,12 +6305,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>621566</t>
+          <t>686948</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Matt Olson</t>
+          <t>Drake Baldwin</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -5651,14 +6335,26 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Aaron Nola</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>605400</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
       <c r="L3" t="n">
-        <v>55.6</v>
+        <v>57.4</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -5672,26 +6368,26 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot</t>
+          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P3" t="n">
-        <v>65.2</v>
+        <v>56.6</v>
       </c>
       <c r="Q3" t="n">
-        <v>41.2</v>
+        <v>47.8</v>
       </c>
       <c r="R3" t="n">
         <v>30.9</v>
       </c>
       <c r="S3" t="n">
-        <v>92.09999999999999</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="T3" t="n">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="U3" t="n">
-        <v>25.3</v>
+        <v>55.3</v>
       </c>
       <c r="V3" t="inlineStr">
         <is>
@@ -5705,7 +6401,7 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -5730,7 +6426,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD3" t="inlineStr"/>
@@ -5747,12 +6443,12 @@
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>11</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>30</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
@@ -5762,90 +6458,114 @@
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/24, 1 HR</t>
+          <t>Contact streak: 11/30 over last 7 games</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 9.2% barrel, 31.3 HR allowed</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>EV profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>14.26</t>
+          <t>12.33</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>52.39</t>
+          <t>50.3</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>92.74</t>
+          <t>91.56</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>103.6622</t>
+          <t>102.2364</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>0.4997</t>
+          <t>0.4975</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
         <is>
-          <t>0.2524</t>
+          <t>0.2206</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>0.3537</t>
+          <t>0.3649</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
         <is>
-          <t>74.53</t>
+          <t>75.3</t>
         </is>
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>47.33</t>
+          <t>56.58</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>37.44</t>
+          <t>32.15</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>33.27</t>
+          <t>25.88</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>37.4</t>
+          <t>23.2</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>0.2393</t>
-        </is>
-      </c>
-      <c r="BA3" t="inlineStr"/>
-      <c r="BB3" t="inlineStr"/>
-      <c r="BC3" t="inlineStr"/>
-      <c r="BD3" t="inlineStr"/>
-      <c r="BE3" t="inlineStr"/>
-      <c r="BF3" t="inlineStr"/>
+          <t>0.181</t>
+        </is>
+      </c>
+      <c r="BA3" t="inlineStr">
+        <is>
+          <t>9.24</t>
+        </is>
+      </c>
+      <c r="BB3" t="inlineStr">
+        <is>
+          <t>41.2</t>
+        </is>
+      </c>
+      <c r="BC3" t="inlineStr">
+        <is>
+          <t>88.77</t>
+        </is>
+      </c>
+      <c r="BD3" t="inlineStr">
+        <is>
+          <t>0.4184</t>
+        </is>
+      </c>
+      <c r="BE3" t="inlineStr">
+        <is>
+          <t>0.1745</t>
+        </is>
+      </c>
+      <c r="BF3" t="inlineStr">
+        <is>
+          <t>27.39</t>
+        </is>
+      </c>
       <c r="BG3" t="inlineStr"/>
       <c r="BH3" t="inlineStr"/>
       <c r="BI3" t="inlineStr">
@@ -5894,11 +6614,23 @@
           <t>2</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Aaron Nola</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>605400</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
       <c r="L4" t="n">
-        <v>55.3</v>
+        <v>56</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
@@ -5919,7 +6651,7 @@
         <v>58.7</v>
       </c>
       <c r="Q4" t="n">
-        <v>41.2</v>
+        <v>47.8</v>
       </c>
       <c r="R4" t="n">
         <v>30.9</v>
@@ -5928,7 +6660,7 @@
         <v>95.5</v>
       </c>
       <c r="T4" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="U4" t="n">
         <v>53.3</v>
@@ -5970,7 +6702,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD4" t="inlineStr"/>
@@ -6007,7 +6739,7 @@
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 9.2% barrel, 31.3 HR allowed</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
@@ -6080,12 +6812,36 @@
           <t>0.2056</t>
         </is>
       </c>
-      <c r="BA4" t="inlineStr"/>
-      <c r="BB4" t="inlineStr"/>
-      <c r="BC4" t="inlineStr"/>
-      <c r="BD4" t="inlineStr"/>
-      <c r="BE4" t="inlineStr"/>
-      <c r="BF4" t="inlineStr"/>
+      <c r="BA4" t="inlineStr">
+        <is>
+          <t>9.24</t>
+        </is>
+      </c>
+      <c r="BB4" t="inlineStr">
+        <is>
+          <t>41.2</t>
+        </is>
+      </c>
+      <c r="BC4" t="inlineStr">
+        <is>
+          <t>88.77</t>
+        </is>
+      </c>
+      <c r="BD4" t="inlineStr">
+        <is>
+          <t>0.4184</t>
+        </is>
+      </c>
+      <c r="BE4" t="inlineStr">
+        <is>
+          <t>0.1745</t>
+        </is>
+      </c>
+      <c r="BF4" t="inlineStr">
+        <is>
+          <t>27.39</t>
+        </is>
+      </c>
       <c r="BG4" t="inlineStr"/>
       <c r="BH4" t="inlineStr"/>
       <c r="BI4" t="inlineStr">
@@ -6101,12 +6857,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>686948</t>
+          <t>671739</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Drake Baldwin</t>
+          <t>Michael Harris</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -6131,14 +6887,26 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Aaron Nola</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>605400</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
       <c r="L5" t="n">
-        <v>54</v>
+        <v>52.2</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -6152,26 +6920,26 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot</t>
+          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P5" t="n">
-        <v>56.6</v>
+        <v>45.1</v>
       </c>
       <c r="Q5" t="n">
-        <v>41.2</v>
+        <v>47.8</v>
       </c>
       <c r="R5" t="n">
         <v>30.9</v>
       </c>
       <c r="S5" t="n">
-        <v>90.40000000000001</v>
+        <v>88.7</v>
       </c>
       <c r="T5" t="n">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="U5" t="n">
-        <v>55.3</v>
+        <v>32</v>
       </c>
       <c r="V5" t="inlineStr">
         <is>
@@ -6185,7 +6953,7 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
@@ -6210,7 +6978,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD5" t="inlineStr"/>
@@ -6227,27 +6995,27 @@
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>Contact streak: 11/30 over last 7 games</t>
+          <t>Contact streak: 9/27 over last 7 games</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 9.2% barrel, 31.3 HR allowed</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
@@ -6257,75 +7025,99 @@
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>12.33</t>
+          <t>9.94</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>50.3</t>
+          <t>46.34</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>91.56</t>
+          <t>90.41</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>102.2364</t>
+          <t>103.0958</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>0.4975</t>
+          <t>0.4653</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
-          <t>0.2206</t>
+          <t>0.1816</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>0.3649</t>
+          <t>0.3339</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
         <is>
-          <t>75.3</t>
+          <t>74.72</t>
         </is>
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>56.58</t>
+          <t>47.05</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>32.15</t>
+          <t>35.66</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>25.88</t>
+          <t>22.42</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>23.2</t>
+          <t>24.2</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>0.181</t>
-        </is>
-      </c>
-      <c r="BA5" t="inlineStr"/>
-      <c r="BB5" t="inlineStr"/>
-      <c r="BC5" t="inlineStr"/>
-      <c r="BD5" t="inlineStr"/>
-      <c r="BE5" t="inlineStr"/>
-      <c r="BF5" t="inlineStr"/>
+          <t>0.1859</t>
+        </is>
+      </c>
+      <c r="BA5" t="inlineStr">
+        <is>
+          <t>9.24</t>
+        </is>
+      </c>
+      <c r="BB5" t="inlineStr">
+        <is>
+          <t>41.2</t>
+        </is>
+      </c>
+      <c r="BC5" t="inlineStr">
+        <is>
+          <t>88.77</t>
+        </is>
+      </c>
+      <c r="BD5" t="inlineStr">
+        <is>
+          <t>0.4184</t>
+        </is>
+      </c>
+      <c r="BE5" t="inlineStr">
+        <is>
+          <t>0.1745</t>
+        </is>
+      </c>
+      <c r="BF5" t="inlineStr">
+        <is>
+          <t>27.39</t>
+        </is>
+      </c>
       <c r="BG5" t="inlineStr"/>
       <c r="BH5" t="inlineStr"/>
       <c r="BI5" t="inlineStr">
@@ -6341,12 +7133,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>547180</t>
+          <t>656941</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Bryce Harper</t>
+          <t>Kyle Schwarber</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -6371,14 +7163,26 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Ray Kerr</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>678061</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
       <c r="L6" t="n">
-        <v>50.6</v>
+        <v>51.9</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -6396,22 +7200,22 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>49</v>
+        <v>73.2</v>
       </c>
       <c r="Q6" t="n">
-        <v>41.2</v>
+        <v>20</v>
       </c>
       <c r="R6" t="n">
         <v>30.9</v>
       </c>
       <c r="S6" t="n">
-        <v>92.09999999999999</v>
+        <v>95.5</v>
       </c>
       <c r="T6" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="U6" t="n">
-        <v>32.5</v>
+        <v>8.1</v>
       </c>
       <c r="V6" t="inlineStr">
         <is>
@@ -6425,7 +7229,7 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
@@ -6450,7 +7254,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:</t>
+          <t>H:2026/2025 P:2026</t>
         </is>
       </c>
       <c r="AD6" t="inlineStr"/>
@@ -6467,105 +7271,129 @@
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>23</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/28, 1 HR</t>
+          <t>Last 7 games: 4/23, 0 HR</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 5.9% barrel, 2.0 HR allowed</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>lift-pull EV profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>10.9</t>
+          <t>17.16</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>44.21</t>
+          <t>52.39</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>90.39</t>
+          <t>92.9</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>101.6293</t>
+          <t>104.176</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>0.4843</t>
+          <t>0.5152</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
-          <t>0.2142</t>
+          <t>0.2756</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>0.3757</t>
+          <t>0.3751</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
         <is>
-          <t>74.1</t>
+          <t>77.16</t>
         </is>
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>45.01</t>
+          <t>75.35</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>38.47</t>
+          <t>54.35</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>26.82</t>
+          <t>32.62</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>28.4</t>
+          <t>48.3</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>0.219</t>
-        </is>
-      </c>
-      <c r="BA6" t="inlineStr"/>
-      <c r="BB6" t="inlineStr"/>
-      <c r="BC6" t="inlineStr"/>
-      <c r="BD6" t="inlineStr"/>
-      <c r="BE6" t="inlineStr"/>
-      <c r="BF6" t="inlineStr"/>
+          <t>0.2866</t>
+        </is>
+      </c>
+      <c r="BA6" t="inlineStr">
+        <is>
+          <t>5.9</t>
+        </is>
+      </c>
+      <c r="BB6" t="inlineStr">
+        <is>
+          <t>31.4</t>
+        </is>
+      </c>
+      <c r="BC6" t="inlineStr">
+        <is>
+          <t>88.0</t>
+        </is>
+      </c>
+      <c r="BD6" t="inlineStr">
+        <is>
+          <t>0.357</t>
+        </is>
+      </c>
+      <c r="BE6" t="inlineStr">
+        <is>
+          <t>0.119</t>
+        </is>
+      </c>
+      <c r="BF6" t="inlineStr">
+        <is>
+          <t>19.6</t>
+        </is>
+      </c>
       <c r="BG6" t="inlineStr"/>
       <c r="BH6" t="inlineStr"/>
       <c r="BI6" t="inlineStr">
@@ -6581,12 +7409,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>671739</t>
+          <t>663586</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Michael Harris</t>
+          <t>Austin Riley</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -6611,14 +7439,26 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Aaron Nola</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>605400</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
       <c r="L7" t="n">
-        <v>48.8</v>
+        <v>47.4</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -6632,26 +7472,26 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot</t>
+          <t>Projected Lineup, Strong Barrel</t>
         </is>
       </c>
       <c r="P7" t="n">
-        <v>45.1</v>
+        <v>53.3</v>
       </c>
       <c r="Q7" t="n">
-        <v>41.2</v>
+        <v>47.8</v>
       </c>
       <c r="R7" t="n">
         <v>30.9</v>
       </c>
       <c r="S7" t="n">
-        <v>88.7</v>
+        <v>47.9</v>
       </c>
       <c r="T7" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="U7" t="n">
-        <v>32</v>
+        <v>48.7</v>
       </c>
       <c r="V7" t="inlineStr">
         <is>
@@ -6665,7 +7505,7 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
@@ -6690,7 +7530,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD7" t="inlineStr"/>
@@ -6707,27 +7547,27 @@
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>Contact streak: 9/27 over last 7 games</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 9.2% barrel, 31.3 HR allowed</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
@@ -6737,75 +7577,99 @@
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>9.94</t>
+          <t>13.24</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>46.34</t>
+          <t>46.07</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>90.41</t>
+          <t>91.6</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>103.0958</t>
+          <t>102.7231</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>0.4653</t>
+          <t>0.4188</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
-          <t>0.1816</t>
+          <t>0.1956</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>0.3339</t>
+          <t>0.3083</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
         <is>
-          <t>74.72</t>
+          <t>75.83</t>
         </is>
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>47.05</t>
+          <t>59.36</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>35.66</t>
+          <t>40.43</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>22.42</t>
+          <t>30.87</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>24.2</t>
+          <t>18.1</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>0.1859</t>
-        </is>
-      </c>
-      <c r="BA7" t="inlineStr"/>
-      <c r="BB7" t="inlineStr"/>
-      <c r="BC7" t="inlineStr"/>
-      <c r="BD7" t="inlineStr"/>
-      <c r="BE7" t="inlineStr"/>
-      <c r="BF7" t="inlineStr"/>
+          <t>0.1519</t>
+        </is>
+      </c>
+      <c r="BA7" t="inlineStr">
+        <is>
+          <t>9.24</t>
+        </is>
+      </c>
+      <c r="BB7" t="inlineStr">
+        <is>
+          <t>41.2</t>
+        </is>
+      </c>
+      <c r="BC7" t="inlineStr">
+        <is>
+          <t>88.77</t>
+        </is>
+      </c>
+      <c r="BD7" t="inlineStr">
+        <is>
+          <t>0.4184</t>
+        </is>
+      </c>
+      <c r="BE7" t="inlineStr">
+        <is>
+          <t>0.1745</t>
+        </is>
+      </c>
+      <c r="BF7" t="inlineStr">
+        <is>
+          <t>27.39</t>
+        </is>
+      </c>
       <c r="BG7" t="inlineStr"/>
       <c r="BH7" t="inlineStr"/>
       <c r="BI7" t="inlineStr">
@@ -6821,24 +7685,24 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>663586</t>
+          <t>547180</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Austin Riley</t>
+          <t>Bryce Harper</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
+          <t>PHI</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
           <t>ATL</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>PHI</t>
-        </is>
-      </c>
       <c r="F8" t="inlineStr">
         <is>
           <t>2026-10-02T00:00:00Z</t>
@@ -6851,14 +7715,26 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Ray Kerr</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>678061</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
       <c r="L8" t="n">
-        <v>46.7</v>
+        <v>44.6</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -6872,26 +7748,26 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel</t>
+          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P8" t="n">
-        <v>53.3</v>
+        <v>49</v>
       </c>
       <c r="Q8" t="n">
-        <v>41.2</v>
+        <v>20</v>
       </c>
       <c r="R8" t="n">
         <v>30.9</v>
       </c>
       <c r="S8" t="n">
-        <v>47.9</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="T8" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="U8" t="n">
-        <v>48.7</v>
+        <v>32.5</v>
       </c>
       <c r="V8" t="inlineStr">
         <is>
@@ -6905,7 +7781,7 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>3</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
@@ -6930,7 +7806,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:</t>
+          <t>H:2026/2025 P:2026</t>
         </is>
       </c>
       <c r="AD8" t="inlineStr"/>
@@ -6947,27 +7823,27 @@
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>28</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Last 7 games: 6/28, 1 HR</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 5.9% barrel, 2.0 HR allowed</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
@@ -6977,75 +7853,99 @@
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>13.24</t>
+          <t>10.9</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>46.07</t>
+          <t>44.21</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>91.6</t>
+          <t>90.39</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>102.7231</t>
+          <t>101.6293</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>0.4188</t>
+          <t>0.4843</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
-          <t>0.1956</t>
+          <t>0.2142</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>0.3083</t>
+          <t>0.3757</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
         <is>
-          <t>75.83</t>
+          <t>74.1</t>
         </is>
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>59.36</t>
+          <t>45.01</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>40.43</t>
+          <t>38.47</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>30.87</t>
+          <t>26.82</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>18.1</t>
+          <t>28.4</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>0.1519</t>
-        </is>
-      </c>
-      <c r="BA8" t="inlineStr"/>
-      <c r="BB8" t="inlineStr"/>
-      <c r="BC8" t="inlineStr"/>
-      <c r="BD8" t="inlineStr"/>
-      <c r="BE8" t="inlineStr"/>
-      <c r="BF8" t="inlineStr"/>
+          <t>0.219</t>
+        </is>
+      </c>
+      <c r="BA8" t="inlineStr">
+        <is>
+          <t>5.9</t>
+        </is>
+      </c>
+      <c r="BB8" t="inlineStr">
+        <is>
+          <t>31.4</t>
+        </is>
+      </c>
+      <c r="BC8" t="inlineStr">
+        <is>
+          <t>88.0</t>
+        </is>
+      </c>
+      <c r="BD8" t="inlineStr">
+        <is>
+          <t>0.357</t>
+        </is>
+      </c>
+      <c r="BE8" t="inlineStr">
+        <is>
+          <t>0.119</t>
+        </is>
+      </c>
+      <c r="BF8" t="inlineStr">
+        <is>
+          <t>19.6</t>
+        </is>
+      </c>
       <c r="BG8" t="inlineStr"/>
       <c r="BH8" t="inlineStr"/>
       <c r="BI8" t="inlineStr">
@@ -7061,24 +7961,24 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>669016</t>
+          <t>573262</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Brandon Marsh</t>
+          <t>Mike Yastrzemski</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
+          <t>ATL</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
           <t>PHI</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>ATL</t>
-        </is>
-      </c>
       <c r="F9" t="inlineStr">
         <is>
           <t>2026-10-02T00:00:00Z</t>
@@ -7091,14 +7991,26 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Aaron Nola</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>605400</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
       <c r="L9" t="n">
-        <v>43.7</v>
+        <v>44.4</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -7112,26 +8024,26 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Projected Lineup, Platoon Edge</t>
         </is>
       </c>
       <c r="P9" t="n">
-        <v>36.1</v>
+        <v>34.7</v>
       </c>
       <c r="Q9" t="n">
-        <v>41.2</v>
+        <v>47.8</v>
       </c>
       <c r="R9" t="n">
         <v>30.9</v>
       </c>
       <c r="S9" t="n">
-        <v>71.7</v>
+        <v>59.8</v>
       </c>
       <c r="T9" t="n">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="U9" t="n">
-        <v>35.6</v>
+        <v>24</v>
       </c>
       <c r="V9" t="inlineStr">
         <is>
@@ -7145,7 +8057,7 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
@@ -7170,7 +8082,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD9" t="inlineStr"/>
@@ -7187,12 +8099,12 @@
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>19</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
@@ -7202,12 +8114,12 @@
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/17, 1 HR</t>
+          <t>Last 7 games: 3/19, 1 HR</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 9.2% barrel, 31.3 HR allowed</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
@@ -7217,75 +8129,99 @@
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>8.12</t>
+          <t>7.31</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>43.74</t>
+          <t>42.88</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>89.77</t>
+          <t>90.52</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>100.0232</t>
+          <t>99.7248</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>0.4103</t>
+          <t>0.3833</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
         <is>
-          <t>0.1564</t>
+          <t>0.1477</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>0.3097</t>
+          <t>0.315</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
         <is>
-          <t>71.54</t>
+          <t>71.24</t>
         </is>
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>15.58</t>
+          <t>8.65</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>38.26</t>
+          <t>43.03</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>26.87</t>
+          <t>30.91</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>15.9</t>
+          <t>13.5</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>0.1525</t>
-        </is>
-      </c>
-      <c r="BA9" t="inlineStr"/>
-      <c r="BB9" t="inlineStr"/>
-      <c r="BC9" t="inlineStr"/>
-      <c r="BD9" t="inlineStr"/>
-      <c r="BE9" t="inlineStr"/>
-      <c r="BF9" t="inlineStr"/>
+          <t>0.1602</t>
+        </is>
+      </c>
+      <c r="BA9" t="inlineStr">
+        <is>
+          <t>9.24</t>
+        </is>
+      </c>
+      <c r="BB9" t="inlineStr">
+        <is>
+          <t>41.2</t>
+        </is>
+      </c>
+      <c r="BC9" t="inlineStr">
+        <is>
+          <t>88.77</t>
+        </is>
+      </c>
+      <c r="BD9" t="inlineStr">
+        <is>
+          <t>0.4184</t>
+        </is>
+      </c>
+      <c r="BE9" t="inlineStr">
+        <is>
+          <t>0.1745</t>
+        </is>
+      </c>
+      <c r="BF9" t="inlineStr">
+        <is>
+          <t>27.39</t>
+        </is>
+      </c>
       <c r="BG9" t="inlineStr"/>
       <c r="BH9" t="inlineStr"/>
       <c r="BI9" t="inlineStr">
@@ -7301,12 +8237,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>681082</t>
+          <t>664761</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Bryson Stott</t>
+          <t>Alec Bohm</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -7331,14 +8267,26 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>Ray Kerr</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>678061</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
       <c r="L10" t="n">
-        <v>42.9</v>
+        <v>39.3</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
@@ -7352,26 +8300,26 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot</t>
+          <t>Projected Lineup, Platoon Edge</t>
         </is>
       </c>
       <c r="P10" t="n">
-        <v>25.2</v>
+        <v>32.7</v>
       </c>
       <c r="Q10" t="n">
-        <v>41.2</v>
+        <v>20</v>
       </c>
       <c r="R10" t="n">
         <v>30.9</v>
       </c>
       <c r="S10" t="n">
-        <v>90.40000000000001</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="T10" t="n">
-        <v>60</v>
+        <v>78</v>
       </c>
       <c r="U10" t="n">
-        <v>40.7</v>
+        <v>10.8</v>
       </c>
       <c r="V10" t="inlineStr">
         <is>
@@ -7385,7 +8333,7 @@
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr">
@@ -7410,7 +8358,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:</t>
+          <t>H:2026/2025 P:2026</t>
         </is>
       </c>
       <c r="AD10" t="inlineStr"/>
@@ -7427,12 +8375,12 @@
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
@@ -7442,12 +8390,12 @@
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>Contact streak: 9/23 over last 7 games</t>
+          <t>Last 7 games: 5/26, 0 HR</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 5.9% barrel, 2.0 HR allowed</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
@@ -7457,75 +8405,99 @@
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>5.66</t>
+          <t>6.06</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>35.24</t>
+          <t>44.58</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>88.86</t>
+          <t>90.66</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>98.4048</t>
+          <t>100.426</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>0.3993</t>
+          <t>0.4123</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
         <is>
-          <t>0.1383</t>
+          <t>0.1446</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>0.3249</t>
+          <t>0.3261</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
         <is>
-          <t>69.72</t>
+          <t>71.28</t>
         </is>
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>6.75</t>
+          <t>15.26</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>34.17</t>
+          <t>28.28</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>27.59</t>
+          <t>22.44</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>10.9</t>
+          <t>13.8</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>0.1417</t>
-        </is>
-      </c>
-      <c r="BA10" t="inlineStr"/>
-      <c r="BB10" t="inlineStr"/>
-      <c r="BC10" t="inlineStr"/>
-      <c r="BD10" t="inlineStr"/>
-      <c r="BE10" t="inlineStr"/>
-      <c r="BF10" t="inlineStr"/>
+          <t>0.1304</t>
+        </is>
+      </c>
+      <c r="BA10" t="inlineStr">
+        <is>
+          <t>5.9</t>
+        </is>
+      </c>
+      <c r="BB10" t="inlineStr">
+        <is>
+          <t>31.4</t>
+        </is>
+      </c>
+      <c r="BC10" t="inlineStr">
+        <is>
+          <t>88.0</t>
+        </is>
+      </c>
+      <c r="BD10" t="inlineStr">
+        <is>
+          <t>0.357</t>
+        </is>
+      </c>
+      <c r="BE10" t="inlineStr">
+        <is>
+          <t>0.119</t>
+        </is>
+      </c>
+      <c r="BF10" t="inlineStr">
+        <is>
+          <t>19.6</t>
+        </is>
+      </c>
       <c r="BG10" t="inlineStr"/>
       <c r="BH10" t="inlineStr"/>
       <c r="BI10" t="inlineStr">
@@ -7541,12 +8513,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>664761</t>
+          <t>607208</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Alec Bohm</t>
+          <t>Trea Turner</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -7571,14 +8543,26 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>Ray Kerr</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>678061</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
       <c r="L11" t="n">
-        <v>42.7</v>
+        <v>38.7</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -7592,26 +8576,26 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P11" t="n">
-        <v>32.7</v>
+        <v>26.4</v>
       </c>
       <c r="Q11" t="n">
-        <v>41.2</v>
+        <v>20</v>
       </c>
       <c r="R11" t="n">
         <v>30.9</v>
       </c>
       <c r="S11" t="n">
-        <v>81.90000000000001</v>
+        <v>88.7</v>
       </c>
       <c r="T11" t="n">
-        <v>60</v>
+        <v>78</v>
       </c>
       <c r="U11" t="n">
-        <v>10.8</v>
+        <v>22</v>
       </c>
       <c r="V11" t="inlineStr">
         <is>
@@ -7625,7 +8609,7 @@
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr">
@@ -7650,7 +8634,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:</t>
+          <t>H:2026/2025 P:2026</t>
         </is>
       </c>
       <c r="AD11" t="inlineStr"/>
@@ -7667,12 +8651,12 @@
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>30</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
@@ -7682,12 +8666,12 @@
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/26, 0 HR</t>
+          <t>Last 7 games: 8/30, 0 HR</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 5.9% barrel, 2.0 HR allowed</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
@@ -7697,75 +8681,99 @@
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>6.06</t>
+          <t>5.94</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>44.58</t>
+          <t>40.14</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>90.66</t>
+          <t>88.74</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>100.426</t>
+          <t>99.2936</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>0.4123</t>
+          <t>0.3771</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
         <is>
-          <t>0.1446</t>
+          <t>0.1267</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>0.3261</t>
+          <t>0.3014</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
         <is>
-          <t>71.28</t>
+          <t>71.45</t>
         </is>
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>15.26</t>
+          <t>18.58</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>28.28</t>
+          <t>35.17</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>22.44</t>
+          <t>24.64</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>13.8</t>
+          <t>17.8</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>0.1304</t>
-        </is>
-      </c>
-      <c r="BA11" t="inlineStr"/>
-      <c r="BB11" t="inlineStr"/>
-      <c r="BC11" t="inlineStr"/>
-      <c r="BD11" t="inlineStr"/>
-      <c r="BE11" t="inlineStr"/>
-      <c r="BF11" t="inlineStr"/>
+          <t>0.1411</t>
+        </is>
+      </c>
+      <c r="BA11" t="inlineStr">
+        <is>
+          <t>5.9</t>
+        </is>
+      </c>
+      <c r="BB11" t="inlineStr">
+        <is>
+          <t>31.4</t>
+        </is>
+      </c>
+      <c r="BC11" t="inlineStr">
+        <is>
+          <t>88.0</t>
+        </is>
+      </c>
+      <c r="BD11" t="inlineStr">
+        <is>
+          <t>0.357</t>
+        </is>
+      </c>
+      <c r="BE11" t="inlineStr">
+        <is>
+          <t>0.119</t>
+        </is>
+      </c>
+      <c r="BF11" t="inlineStr">
+        <is>
+          <t>19.6</t>
+        </is>
+      </c>
       <c r="BG11" t="inlineStr"/>
       <c r="BH11" t="inlineStr"/>
       <c r="BI11" t="inlineStr">
@@ -7781,12 +8789,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>607208</t>
+          <t>624641</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Trea Turner</t>
+          <t>Edmundo Sosa</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -7811,14 +8819,26 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>Ray Kerr</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>678061</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
       <c r="L12" t="n">
-        <v>42.2</v>
+        <v>38.4</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
@@ -7832,26 +8852,26 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot</t>
+          <t>Projected Lineup, Platoon Edge, Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P12" t="n">
-        <v>26.4</v>
+        <v>30.1</v>
       </c>
       <c r="Q12" t="n">
-        <v>41.2</v>
+        <v>20</v>
       </c>
       <c r="R12" t="n">
         <v>30.9</v>
       </c>
       <c r="S12" t="n">
-        <v>88.7</v>
+        <v>59.8</v>
       </c>
       <c r="T12" t="n">
-        <v>60</v>
+        <v>78</v>
       </c>
       <c r="U12" t="n">
-        <v>22</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="V12" t="inlineStr">
         <is>
@@ -7865,7 +8885,7 @@
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>7</t>
         </is>
       </c>
       <c r="Y12" t="inlineStr">
@@ -7890,7 +8910,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:</t>
+          <t>H:2026/2025 P:2026</t>
         </is>
       </c>
       <c r="AD12" t="inlineStr"/>
@@ -7907,27 +8927,27 @@
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>17</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>Last 7 games: 8/30, 0 HR</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 5.9% barrel, 2.0 HR allowed</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
@@ -7937,75 +8957,99 @@
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>5.94</t>
+          <t>6.93</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>40.14</t>
+          <t>38.84</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>88.74</t>
+          <t>87.77</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>99.2936</t>
+          <t>99.9033</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>0.3771</t>
+          <t>0.4281</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
         <is>
-          <t>0.1267</t>
+          <t>0.1614</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>0.3014</t>
+          <t>0.3166</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
         <is>
-          <t>71.45</t>
+          <t>72.44</t>
         </is>
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>18.58</t>
+          <t>27.29</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>35.17</t>
+          <t>41.31</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>24.64</t>
+          <t>21.78</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>17.8</t>
+          <t>9.6</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>0.1411</t>
-        </is>
-      </c>
-      <c r="BA12" t="inlineStr"/>
-      <c r="BB12" t="inlineStr"/>
-      <c r="BC12" t="inlineStr"/>
-      <c r="BD12" t="inlineStr"/>
-      <c r="BE12" t="inlineStr"/>
-      <c r="BF12" t="inlineStr"/>
+          <t>0.1853</t>
+        </is>
+      </c>
+      <c r="BA12" t="inlineStr">
+        <is>
+          <t>5.9</t>
+        </is>
+      </c>
+      <c r="BB12" t="inlineStr">
+        <is>
+          <t>31.4</t>
+        </is>
+      </c>
+      <c r="BC12" t="inlineStr">
+        <is>
+          <t>88.0</t>
+        </is>
+      </c>
+      <c r="BD12" t="inlineStr">
+        <is>
+          <t>0.357</t>
+        </is>
+      </c>
+      <c r="BE12" t="inlineStr">
+        <is>
+          <t>0.119</t>
+        </is>
+      </c>
+      <c r="BF12" t="inlineStr">
+        <is>
+          <t>19.6</t>
+        </is>
+      </c>
       <c r="BG12" t="inlineStr"/>
       <c r="BH12" t="inlineStr"/>
       <c r="BI12" t="inlineStr">
@@ -8021,24 +9065,24 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>624641</t>
+          <t>643289</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Edmundo Sosa</t>
+          <t>Mauricio Dubon</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
+          <t>ATL</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
           <t>PHI</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>ATL</t>
-        </is>
-      </c>
       <c r="F13" t="inlineStr">
         <is>
           <t>2026-10-02T00:00:00Z</t>
@@ -8051,14 +9095,26 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>Aaron Nola</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>605400</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
       <c r="L13" t="n">
-        <v>41.8</v>
+        <v>38</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
@@ -8072,26 +9128,26 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>Projected Lineup, Hot Hitter/Streak</t>
+          <t>Projected Lineup</t>
         </is>
       </c>
       <c r="P13" t="n">
-        <v>30.1</v>
+        <v>10.2</v>
       </c>
       <c r="Q13" t="n">
-        <v>41.2</v>
+        <v>47.8</v>
       </c>
       <c r="R13" t="n">
         <v>30.9</v>
       </c>
       <c r="S13" t="n">
-        <v>59.8</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="T13" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="U13" t="n">
-        <v>71.59999999999999</v>
+        <v>50.3</v>
       </c>
       <c r="V13" t="inlineStr">
         <is>
@@ -8105,7 +9161,7 @@
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr">
@@ -8130,7 +9186,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD13" t="inlineStr"/>
@@ -8147,27 +9203,27 @@
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Contact streak: 9/27 over last 7 games</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 9.2% barrel, 31.3 HR allowed</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
@@ -8177,75 +9233,99 @@
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>6.93</t>
+          <t>3.16</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>38.84</t>
+          <t>28.47</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>87.77</t>
+          <t>85.9</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>99.9033</t>
+          <t>96.2638</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>0.4281</t>
+          <t>0.3618</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
         <is>
-          <t>0.1614</t>
+          <t>0.1008</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>0.3166</t>
+          <t>0.2962</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
         <is>
-          <t>72.44</t>
+          <t>68.87</t>
         </is>
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>27.29</t>
+          <t>4.1</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>41.31</t>
+          <t>31.89</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>21.78</t>
+          <t>25.86</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>9.6</t>
+          <t>10.5</t>
         </is>
       </c>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>0.1853</t>
-        </is>
-      </c>
-      <c r="BA13" t="inlineStr"/>
-      <c r="BB13" t="inlineStr"/>
-      <c r="BC13" t="inlineStr"/>
-      <c r="BD13" t="inlineStr"/>
-      <c r="BE13" t="inlineStr"/>
-      <c r="BF13" t="inlineStr"/>
+          <t>0.1203</t>
+        </is>
+      </c>
+      <c r="BA13" t="inlineStr">
+        <is>
+          <t>9.24</t>
+        </is>
+      </c>
+      <c r="BB13" t="inlineStr">
+        <is>
+          <t>41.2</t>
+        </is>
+      </c>
+      <c r="BC13" t="inlineStr">
+        <is>
+          <t>88.77</t>
+        </is>
+      </c>
+      <c r="BD13" t="inlineStr">
+        <is>
+          <t>0.4184</t>
+        </is>
+      </c>
+      <c r="BE13" t="inlineStr">
+        <is>
+          <t>0.1745</t>
+        </is>
+      </c>
+      <c r="BF13" t="inlineStr">
+        <is>
+          <t>27.39</t>
+        </is>
+      </c>
       <c r="BG13" t="inlineStr"/>
       <c r="BH13" t="inlineStr"/>
       <c r="BI13" t="inlineStr">
@@ -8261,12 +9341,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>573262</t>
+          <t>645277</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Mike Yastrzemski</t>
+          <t>Ozzie Albies</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -8291,14 +9371,26 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>Aaron Nola</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>605400</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
       <c r="L14" t="n">
-        <v>41</v>
+        <v>37.8</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
@@ -8312,26 +9404,26 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Projected Lineup, Platoon Edge</t>
         </is>
       </c>
       <c r="P14" t="n">
-        <v>34.7</v>
+        <v>15.3</v>
       </c>
       <c r="Q14" t="n">
-        <v>41.2</v>
+        <v>47.3</v>
       </c>
       <c r="R14" t="n">
         <v>30.9</v>
       </c>
       <c r="S14" t="n">
-        <v>59.8</v>
+        <v>71.7</v>
       </c>
       <c r="T14" t="n">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="U14" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="V14" t="inlineStr">
         <is>
@@ -8345,7 +9437,7 @@
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="Y14" t="inlineStr">
@@ -8370,7 +9462,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD14" t="inlineStr"/>
@@ -8392,22 +9484,22 @@
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>Last 7 games: 3/19, 1 HR</t>
+          <t>Last 7 games: 3/25, 0 HR</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>switch hitter; pitcher baseline 9.2% barrel, 31.3 HR allowed</t>
         </is>
       </c>
       <c r="AM14" t="inlineStr">
@@ -8417,75 +9509,99 @@
       </c>
       <c r="AN14" t="inlineStr">
         <is>
-          <t>7.31</t>
+          <t>4.13</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>42.88</t>
+          <t>28.6</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>90.52</t>
+          <t>87.22</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>99.7248</t>
+          <t>96.687</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>0.3833</t>
+          <t>0.346</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
         <is>
-          <t>0.1477</t>
+          <t>0.1184</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>0.315</t>
+          <t>0.2808</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
         <is>
-          <t>71.24</t>
+          <t>68.86</t>
         </is>
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>8.65</t>
+          <t>5.67</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>43.03</t>
+          <t>46.7</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>30.91</t>
+          <t>31.48</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>13.5</t>
+          <t>20.2</t>
         </is>
       </c>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>0.1602</t>
-        </is>
-      </c>
-      <c r="BA14" t="inlineStr"/>
-      <c r="BB14" t="inlineStr"/>
-      <c r="BC14" t="inlineStr"/>
-      <c r="BD14" t="inlineStr"/>
-      <c r="BE14" t="inlineStr"/>
-      <c r="BF14" t="inlineStr"/>
+          <t>0.146</t>
+        </is>
+      </c>
+      <c r="BA14" t="inlineStr">
+        <is>
+          <t>9.24</t>
+        </is>
+      </c>
+      <c r="BB14" t="inlineStr">
+        <is>
+          <t>41.2</t>
+        </is>
+      </c>
+      <c r="BC14" t="inlineStr">
+        <is>
+          <t>88.77</t>
+        </is>
+      </c>
+      <c r="BD14" t="inlineStr">
+        <is>
+          <t>0.4184</t>
+        </is>
+      </c>
+      <c r="BE14" t="inlineStr">
+        <is>
+          <t>0.1745</t>
+        </is>
+      </c>
+      <c r="BF14" t="inlineStr">
+        <is>
+          <t>27.39</t>
+        </is>
+      </c>
       <c r="BG14" t="inlineStr"/>
       <c r="BH14" t="inlineStr"/>
       <c r="BI14" t="inlineStr">
@@ -8501,24 +9617,24 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>643289</t>
+          <t>669016</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Mauricio Dubon</t>
+          <t>Brandon Marsh</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
+          <t>PHI</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
           <t>ATL</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>PHI</t>
-        </is>
-      </c>
       <c r="F15" t="inlineStr">
         <is>
           <t>2026-10-02T00:00:00Z</t>
@@ -8531,14 +9647,26 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>Ray Kerr</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>678061</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
       <c r="L15" t="n">
-        <v>37.3</v>
+        <v>37.7</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
@@ -8556,22 +9684,22 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>10.2</v>
+        <v>36.1</v>
       </c>
       <c r="Q15" t="n">
-        <v>41.2</v>
+        <v>20</v>
       </c>
       <c r="R15" t="n">
         <v>30.9</v>
       </c>
       <c r="S15" t="n">
-        <v>81.90000000000001</v>
+        <v>71.7</v>
       </c>
       <c r="T15" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="U15" t="n">
-        <v>50.3</v>
+        <v>35.6</v>
       </c>
       <c r="V15" t="inlineStr">
         <is>
@@ -8585,7 +9713,7 @@
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="Y15" t="inlineStr">
@@ -8610,7 +9738,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:</t>
+          <t>H:2026/2025 P:2026</t>
         </is>
       </c>
       <c r="AD15" t="inlineStr"/>
@@ -8627,12 +9755,12 @@
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>17</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
@@ -8642,12 +9770,12 @@
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>Contact streak: 9/27 over last 7 games</t>
+          <t>Last 7 games: 4/17, 1 HR</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 5.9% barrel, 2.0 HR allowed</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
@@ -8657,75 +9785,99 @@
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>3.16</t>
+          <t>8.12</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>28.47</t>
+          <t>43.74</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>85.9</t>
+          <t>89.77</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>96.2638</t>
+          <t>100.0232</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>0.3618</t>
+          <t>0.4103</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
         <is>
-          <t>0.1008</t>
+          <t>0.1564</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>0.2962</t>
+          <t>0.3097</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
         <is>
-          <t>68.87</t>
+          <t>71.54</t>
         </is>
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>4.1</t>
+          <t>15.58</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>31.89</t>
+          <t>38.26</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>25.86</t>
+          <t>26.87</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>10.5</t>
+          <t>15.9</t>
         </is>
       </c>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>0.1203</t>
-        </is>
-      </c>
-      <c r="BA15" t="inlineStr"/>
-      <c r="BB15" t="inlineStr"/>
-      <c r="BC15" t="inlineStr"/>
-      <c r="BD15" t="inlineStr"/>
-      <c r="BE15" t="inlineStr"/>
-      <c r="BF15" t="inlineStr"/>
+          <t>0.1525</t>
+        </is>
+      </c>
+      <c r="BA15" t="inlineStr">
+        <is>
+          <t>5.9</t>
+        </is>
+      </c>
+      <c r="BB15" t="inlineStr">
+        <is>
+          <t>31.4</t>
+        </is>
+      </c>
+      <c r="BC15" t="inlineStr">
+        <is>
+          <t>88.0</t>
+        </is>
+      </c>
+      <c r="BD15" t="inlineStr">
+        <is>
+          <t>0.357</t>
+        </is>
+      </c>
+      <c r="BE15" t="inlineStr">
+        <is>
+          <t>0.119</t>
+        </is>
+      </c>
+      <c r="BF15" t="inlineStr">
+        <is>
+          <t>19.6</t>
+        </is>
+      </c>
       <c r="BG15" t="inlineStr"/>
       <c r="BH15" t="inlineStr"/>
       <c r="BI15" t="inlineStr">
@@ -8774,11 +9926,23 @@
           <t>9</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>Aaron Nola</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>605400</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
       <c r="L16" t="n">
-        <v>37</v>
+        <v>37.6</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
@@ -8799,7 +9963,7 @@
         <v>34</v>
       </c>
       <c r="Q16" t="n">
-        <v>41.2</v>
+        <v>47.8</v>
       </c>
       <c r="R16" t="n">
         <v>30.9</v>
@@ -8808,7 +9972,7 @@
         <v>40.2</v>
       </c>
       <c r="T16" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="U16" t="n">
         <v>3.4</v>
@@ -8850,7 +10014,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD16" t="inlineStr"/>
@@ -8887,7 +10051,7 @@
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 9.2% barrel, 31.3 HR allowed</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
@@ -8960,12 +10124,36 @@
           <t>0.1456</t>
         </is>
       </c>
-      <c r="BA16" t="inlineStr"/>
-      <c r="BB16" t="inlineStr"/>
-      <c r="BC16" t="inlineStr"/>
-      <c r="BD16" t="inlineStr"/>
-      <c r="BE16" t="inlineStr"/>
-      <c r="BF16" t="inlineStr"/>
+      <c r="BA16" t="inlineStr">
+        <is>
+          <t>9.24</t>
+        </is>
+      </c>
+      <c r="BB16" t="inlineStr">
+        <is>
+          <t>41.2</t>
+        </is>
+      </c>
+      <c r="BC16" t="inlineStr">
+        <is>
+          <t>88.77</t>
+        </is>
+      </c>
+      <c r="BD16" t="inlineStr">
+        <is>
+          <t>0.4184</t>
+        </is>
+      </c>
+      <c r="BE16" t="inlineStr">
+        <is>
+          <t>0.1745</t>
+        </is>
+      </c>
+      <c r="BF16" t="inlineStr">
+        <is>
+          <t>27.39</t>
+        </is>
+      </c>
       <c r="BG16" t="inlineStr"/>
       <c r="BH16" t="inlineStr"/>
       <c r="BI16" t="inlineStr">
@@ -8981,12 +10169,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>592663</t>
+          <t>681082</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>J.T. Realmuto</t>
+          <t>Bryson Stott</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -9011,14 +10199,26 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>Ray Kerr</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>678061</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
       <c r="L17" t="n">
-        <v>36.1</v>
+        <v>36.9</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
@@ -9032,26 +10232,26 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Projected Lineup, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P17" t="n">
-        <v>32</v>
+        <v>25.2</v>
       </c>
       <c r="Q17" t="n">
-        <v>41.2</v>
+        <v>20</v>
       </c>
       <c r="R17" t="n">
         <v>30.9</v>
       </c>
       <c r="S17" t="n">
-        <v>40.2</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="T17" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>40.7</v>
       </c>
       <c r="V17" t="inlineStr">
         <is>
@@ -9065,7 +10265,7 @@
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>4</t>
         </is>
       </c>
       <c r="Y17" t="inlineStr">
@@ -9090,7 +10290,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:</t>
+          <t>H:2026/2025 P:2026</t>
         </is>
       </c>
       <c r="AD17" t="inlineStr"/>
@@ -9107,12 +10307,12 @@
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>23</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
@@ -9122,12 +10322,12 @@
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>Last 7 games: 1/21, 0 HR</t>
+          <t>Contact streak: 9/23 over last 7 games</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 5.9% barrel, 2.0 HR allowed</t>
         </is>
       </c>
       <c r="AM17" t="inlineStr">
@@ -9137,75 +10337,99 @@
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>6.63</t>
+          <t>5.66</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>41.65</t>
+          <t>35.24</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>89.65</t>
+          <t>88.86</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>100.1126</t>
+          <t>98.4048</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>0.3942</t>
+          <t>0.3993</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
         <is>
-          <t>0.144</t>
+          <t>0.1383</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>0.3167</t>
+          <t>0.3249</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
         <is>
-          <t>72.77</t>
+          <t>69.72</t>
         </is>
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>30.54</t>
+          <t>6.75</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>41.39</t>
+          <t>34.17</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>25.94</t>
+          <t>27.59</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>11.3</t>
+          <t>10.9</t>
         </is>
       </c>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>0.1263</t>
-        </is>
-      </c>
-      <c r="BA17" t="inlineStr"/>
-      <c r="BB17" t="inlineStr"/>
-      <c r="BC17" t="inlineStr"/>
-      <c r="BD17" t="inlineStr"/>
-      <c r="BE17" t="inlineStr"/>
-      <c r="BF17" t="inlineStr"/>
+          <t>0.1417</t>
+        </is>
+      </c>
+      <c r="BA17" t="inlineStr">
+        <is>
+          <t>5.9</t>
+        </is>
+      </c>
+      <c r="BB17" t="inlineStr">
+        <is>
+          <t>31.4</t>
+        </is>
+      </c>
+      <c r="BC17" t="inlineStr">
+        <is>
+          <t>88.0</t>
+        </is>
+      </c>
+      <c r="BD17" t="inlineStr">
+        <is>
+          <t>0.357</t>
+        </is>
+      </c>
+      <c r="BE17" t="inlineStr">
+        <is>
+          <t>0.119</t>
+        </is>
+      </c>
+      <c r="BF17" t="inlineStr">
+        <is>
+          <t>19.6</t>
+        </is>
+      </c>
       <c r="BG17" t="inlineStr"/>
       <c r="BH17" t="inlineStr"/>
       <c r="BI17" t="inlineStr">
@@ -9221,24 +10445,24 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>645277</t>
+          <t>592663</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Ozzie Albies</t>
+          <t>J.T. Realmuto</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
+          <t>PHI</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
           <t>ATL</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>PHI</t>
-        </is>
-      </c>
       <c r="F18" t="inlineStr">
         <is>
           <t>2026-10-02T00:00:00Z</t>
@@ -9251,14 +10475,26 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>Ray Kerr</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>678061</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
       <c r="L18" t="n">
-        <v>36.1</v>
+        <v>32.7</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
@@ -9276,19 +10512,19 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>15.3</v>
+        <v>32</v>
       </c>
       <c r="Q18" t="n">
-        <v>40.2</v>
+        <v>20</v>
       </c>
       <c r="R18" t="n">
         <v>30.9</v>
       </c>
       <c r="S18" t="n">
-        <v>71.7</v>
+        <v>40.2</v>
       </c>
       <c r="T18" t="n">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="U18" t="n">
         <v>0</v>
@@ -9305,7 +10541,7 @@
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>9</t>
         </is>
       </c>
       <c r="Y18" t="inlineStr">
@@ -9330,7 +10566,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:</t>
+          <t>H:2026/2025 P:2026</t>
         </is>
       </c>
       <c r="AD18" t="inlineStr"/>
@@ -9347,12 +10583,12 @@
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
@@ -9362,12 +10598,12 @@
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>Last 7 games: 3/25, 0 HR</t>
+          <t>Last 7 games: 1/21, 0 HR</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 5.9% barrel, 2.0 HR allowed</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
@@ -9377,75 +10613,99 @@
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>4.13</t>
+          <t>6.63</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>28.6</t>
+          <t>41.65</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>87.22</t>
+          <t>89.65</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>96.687</t>
+          <t>100.1126</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>0.346</t>
+          <t>0.3942</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
         <is>
-          <t>0.1184</t>
+          <t>0.144</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>0.2808</t>
+          <t>0.3167</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
         <is>
-          <t>68.86</t>
+          <t>72.77</t>
         </is>
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>5.67</t>
+          <t>30.54</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>46.7</t>
+          <t>41.39</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>31.48</t>
+          <t>25.94</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>20.2</t>
+          <t>11.3</t>
         </is>
       </c>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>0.146</t>
-        </is>
-      </c>
-      <c r="BA18" t="inlineStr"/>
-      <c r="BB18" t="inlineStr"/>
-      <c r="BC18" t="inlineStr"/>
-      <c r="BD18" t="inlineStr"/>
-      <c r="BE18" t="inlineStr"/>
-      <c r="BF18" t="inlineStr"/>
+          <t>0.1263</t>
+        </is>
+      </c>
+      <c r="BA18" t="inlineStr">
+        <is>
+          <t>5.9</t>
+        </is>
+      </c>
+      <c r="BB18" t="inlineStr">
+        <is>
+          <t>31.4</t>
+        </is>
+      </c>
+      <c r="BC18" t="inlineStr">
+        <is>
+          <t>88.0</t>
+        </is>
+      </c>
+      <c r="BD18" t="inlineStr">
+        <is>
+          <t>0.357</t>
+        </is>
+      </c>
+      <c r="BE18" t="inlineStr">
+        <is>
+          <t>0.119</t>
+        </is>
+      </c>
+      <c r="BF18" t="inlineStr">
+        <is>
+          <t>19.6</t>
+        </is>
+      </c>
       <c r="BG18" t="inlineStr"/>
       <c r="BH18" t="inlineStr"/>
       <c r="BI18" t="inlineStr">
@@ -9494,11 +10754,23 @@
           <t>8</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>Ray Kerr</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>678061</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
       <c r="L19" t="n">
-        <v>31.1</v>
+        <v>25.1</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
@@ -9519,7 +10791,7 @@
         <v>10.9</v>
       </c>
       <c r="Q19" t="n">
-        <v>41.2</v>
+        <v>20</v>
       </c>
       <c r="R19" t="n">
         <v>30.9</v>
@@ -9528,7 +10800,7 @@
         <v>47.9</v>
       </c>
       <c r="T19" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="U19" t="n">
         <v>17.7</v>
@@ -9570,7 +10842,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>H:2026 P:</t>
+          <t>H:2026 P:2026</t>
         </is>
       </c>
       <c r="AD19" t="inlineStr"/>
@@ -9607,7 +10879,7 @@
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 5.9% barrel, 2.0 HR allowed</t>
         </is>
       </c>
       <c r="AM19" t="inlineStr">
@@ -9680,12 +10952,36 @@
           <t>0.089</t>
         </is>
       </c>
-      <c r="BA19" t="inlineStr"/>
-      <c r="BB19" t="inlineStr"/>
-      <c r="BC19" t="inlineStr"/>
-      <c r="BD19" t="inlineStr"/>
-      <c r="BE19" t="inlineStr"/>
-      <c r="BF19" t="inlineStr"/>
+      <c r="BA19" t="inlineStr">
+        <is>
+          <t>5.9</t>
+        </is>
+      </c>
+      <c r="BB19" t="inlineStr">
+        <is>
+          <t>31.4</t>
+        </is>
+      </c>
+      <c r="BC19" t="inlineStr">
+        <is>
+          <t>88.0</t>
+        </is>
+      </c>
+      <c r="BD19" t="inlineStr">
+        <is>
+          <t>0.357</t>
+        </is>
+      </c>
+      <c r="BE19" t="inlineStr">
+        <is>
+          <t>0.119</t>
+        </is>
+      </c>
+      <c r="BF19" t="inlineStr">
+        <is>
+          <t>19.6</t>
+        </is>
+      </c>
       <c r="BG19" t="inlineStr"/>
       <c r="BH19" t="inlineStr"/>
       <c r="BI19" t="inlineStr">

--- a/outputs/daily/hr_rankings_2026-10-01.xlsx
+++ b/outputs/daily/hr_rankings_2026-10-01.xlsx
@@ -760,7 +760,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -784,11 +784,11 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>59</v>
+        <v>62.9</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>Longshot</t>
+          <t>Tier 3</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -798,7 +798,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P2" t="n">
@@ -808,10 +808,10 @@
         <v>47.8</v>
       </c>
       <c r="R2" t="n">
-        <v>30.9</v>
+        <v>52.9</v>
       </c>
       <c r="S2" t="n">
-        <v>92.09999999999999</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="T2" t="n">
         <v>80</v>
@@ -821,39 +821,35 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr"/>
       <c r="AC2" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -996,8 +992,16 @@
           <t>27.39</t>
         </is>
       </c>
-      <c r="BG2" t="inlineStr"/>
-      <c r="BH2" t="inlineStr"/>
+      <c r="BG2" t="inlineStr">
+        <is>
+          <t>L To R</t>
+        </is>
+      </c>
+      <c r="BH2" t="inlineStr">
+        <is>
+          <t>79</t>
+        </is>
+      </c>
       <c r="BI2" t="inlineStr">
         <is>
           <t>Truist Park</t>
@@ -1036,12 +1040,12 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -1060,11 +1064,11 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>57.4</v>
+        <v>61.1</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>Longshot</t>
+          <t>Tier 3</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -1074,7 +1078,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P3" t="n">
@@ -1084,10 +1088,10 @@
         <v>47.8</v>
       </c>
       <c r="R3" t="n">
-        <v>30.9</v>
+        <v>52.9</v>
       </c>
       <c r="S3" t="n">
-        <v>90.40000000000001</v>
+        <v>93.2</v>
       </c>
       <c r="T3" t="n">
         <v>80</v>
@@ -1097,39 +1101,35 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr"/>
       <c r="AC3" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -1272,8 +1272,16 @@
           <t>27.39</t>
         </is>
       </c>
-      <c r="BG3" t="inlineStr"/>
-      <c r="BH3" t="inlineStr"/>
+      <c r="BG3" t="inlineStr">
+        <is>
+          <t>L To R</t>
+        </is>
+      </c>
+      <c r="BH3" t="inlineStr">
+        <is>
+          <t>79</t>
+        </is>
+      </c>
       <c r="BI3" t="inlineStr">
         <is>
           <t>Truist Park</t>
@@ -1292,7 +1300,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Ronald Acuna</t>
+          <t>Ronald Acuña Jr.</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1312,7 +1320,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -1336,7 +1344,7 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
@@ -1350,7 +1358,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot</t>
+          <t>Strong Barrel, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P4" t="n">
@@ -1360,10 +1368,10 @@
         <v>47.8</v>
       </c>
       <c r="R4" t="n">
-        <v>30.9</v>
+        <v>52.9</v>
       </c>
       <c r="S4" t="n">
-        <v>95.5</v>
+        <v>100</v>
       </c>
       <c r="T4" t="n">
         <v>50</v>
@@ -1373,39 +1381,35 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr"/>
       <c r="AC4" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -1548,8 +1552,16 @@
           <t>27.39</t>
         </is>
       </c>
-      <c r="BG4" t="inlineStr"/>
-      <c r="BH4" t="inlineStr"/>
+      <c r="BG4" t="inlineStr">
+        <is>
+          <t>L To R</t>
+        </is>
+      </c>
+      <c r="BH4" t="inlineStr">
+        <is>
+          <t>79</t>
+        </is>
+      </c>
       <c r="BI4" t="inlineStr">
         <is>
           <t>Truist Park</t>
@@ -1568,7 +1580,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Michael Harris</t>
+          <t>Michael Harris II</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1588,12 +1600,12 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1612,7 +1624,7 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>52.2</v>
+        <v>56.4</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -1626,7 +1638,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P5" t="n">
@@ -1636,10 +1648,10 @@
         <v>47.8</v>
       </c>
       <c r="R5" t="n">
-        <v>30.9</v>
+        <v>52.9</v>
       </c>
       <c r="S5" t="n">
-        <v>88.7</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="T5" t="n">
         <v>80</v>
@@ -1649,39 +1661,35 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr"/>
       <c r="AC5" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -1824,8 +1832,16 @@
           <t>27.39</t>
         </is>
       </c>
-      <c r="BG5" t="inlineStr"/>
-      <c r="BH5" t="inlineStr"/>
+      <c r="BG5" t="inlineStr">
+        <is>
+          <t>L To R</t>
+        </is>
+      </c>
+      <c r="BH5" t="inlineStr">
+        <is>
+          <t>79</t>
+        </is>
+      </c>
       <c r="BI5" t="inlineStr">
         <is>
           <t>Truist Park</t>
@@ -1864,7 +1880,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1888,7 +1904,7 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>51.9</v>
+        <v>55.8</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -1902,7 +1918,7 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot</t>
+          <t>Strong Barrel, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P6" t="n">
@@ -1912,10 +1928,10 @@
         <v>20</v>
       </c>
       <c r="R6" t="n">
-        <v>30.9</v>
+        <v>52.9</v>
       </c>
       <c r="S6" t="n">
-        <v>95.5</v>
+        <v>100</v>
       </c>
       <c r="T6" t="n">
         <v>50</v>
@@ -1925,39 +1941,35 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr"/>
       <c r="AC6" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026</t>
@@ -2100,8 +2112,16 @@
           <t>19.6</t>
         </is>
       </c>
-      <c r="BG6" t="inlineStr"/>
-      <c r="BH6" t="inlineStr"/>
+      <c r="BG6" t="inlineStr">
+        <is>
+          <t>L To R</t>
+        </is>
+      </c>
+      <c r="BH6" t="inlineStr">
+        <is>
+          <t>79</t>
+        </is>
+      </c>
       <c r="BI6" t="inlineStr">
         <is>
           <t>Truist Park</t>
@@ -2140,12 +2160,12 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -2164,7 +2184,7 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>47.4</v>
+        <v>53</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -2178,7 +2198,7 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel</t>
+          <t>Strong Barrel</t>
         </is>
       </c>
       <c r="P7" t="n">
@@ -2188,10 +2208,10 @@
         <v>47.8</v>
       </c>
       <c r="R7" t="n">
-        <v>30.9</v>
+        <v>52.9</v>
       </c>
       <c r="S7" t="n">
-        <v>47.9</v>
+        <v>64.3</v>
       </c>
       <c r="T7" t="n">
         <v>50</v>
@@ -2201,39 +2221,35 @@
       </c>
       <c r="V7" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr"/>
       <c r="AC7" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -2376,8 +2392,16 @@
           <t>27.39</t>
         </is>
       </c>
-      <c r="BG7" t="inlineStr"/>
-      <c r="BH7" t="inlineStr"/>
+      <c r="BG7" t="inlineStr">
+        <is>
+          <t>L To R</t>
+        </is>
+      </c>
+      <c r="BH7" t="inlineStr">
+        <is>
+          <t>79</t>
+        </is>
+      </c>
       <c r="BI7" t="inlineStr">
         <is>
           <t>Truist Park</t>
@@ -2391,24 +2415,24 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>547180</t>
+          <t>573262</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Bryce Harper</t>
+          <t>Mike Yastrzemski</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
+          <t>ATL</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
           <t>PHI</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>ATL</t>
-        </is>
-      </c>
       <c r="F8" t="inlineStr">
         <is>
           <t>2026-10-02T00:00:00Z</t>
@@ -2416,31 +2440,31 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Ray Kerr</t>
+          <t>Aaron Nola</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>678061</t>
+          <t>605400</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L8" t="n">
-        <v>44.6</v>
+        <v>49.9</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -2454,65 +2478,61 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P8" t="n">
-        <v>49</v>
+        <v>34.7</v>
       </c>
       <c r="Q8" t="n">
-        <v>20</v>
+        <v>47.8</v>
       </c>
       <c r="R8" t="n">
-        <v>30.9</v>
+        <v>52.9</v>
       </c>
       <c r="S8" t="n">
-        <v>92.09999999999999</v>
+        <v>76.2</v>
       </c>
       <c r="T8" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U8" t="n">
-        <v>32.5</v>
+        <v>24</v>
       </c>
       <c r="V8" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr"/>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD8" t="inlineStr"/>
@@ -2529,12 +2549,12 @@
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>19</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
@@ -2544,12 +2564,12 @@
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/28, 1 HR</t>
+          <t>Last 7 games: 3/19, 1 HR</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 5.9% barrel, 2.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 9.2% barrel, 31.3 HR allowed</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
@@ -2559,101 +2579,109 @@
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>10.9</t>
+          <t>7.31</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>44.21</t>
+          <t>42.88</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>90.39</t>
+          <t>90.52</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>101.6293</t>
+          <t>99.7248</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>0.4843</t>
+          <t>0.3833</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
-          <t>0.2142</t>
+          <t>0.1477</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>0.3757</t>
+          <t>0.315</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
         <is>
-          <t>74.1</t>
+          <t>71.24</t>
         </is>
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>45.01</t>
+          <t>8.65</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>38.47</t>
+          <t>43.03</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>26.82</t>
+          <t>30.91</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>28.4</t>
+          <t>13.5</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>0.219</t>
+          <t>0.1602</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>5.9</t>
+          <t>9.24</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>31.4</t>
+          <t>41.2</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>88.77</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>0.357</t>
+          <t>0.4184</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
-          <t>0.119</t>
+          <t>0.1745</t>
         </is>
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>19.6</t>
-        </is>
-      </c>
-      <c r="BG8" t="inlineStr"/>
-      <c r="BH8" t="inlineStr"/>
+          <t>27.39</t>
+        </is>
+      </c>
+      <c r="BG8" t="inlineStr">
+        <is>
+          <t>L To R</t>
+        </is>
+      </c>
+      <c r="BH8" t="inlineStr">
+        <is>
+          <t>79</t>
+        </is>
+      </c>
       <c r="BI8" t="inlineStr">
         <is>
           <t>Truist Park</t>
@@ -2667,24 +2695,24 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>573262</t>
+          <t>547180</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Mike Yastrzemski</t>
+          <t>Bryce Harper</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
+          <t>PHI</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
           <t>ATL</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>PHI</t>
-        </is>
-      </c>
       <c r="F9" t="inlineStr">
         <is>
           <t>2026-10-02T00:00:00Z</t>
@@ -2692,31 +2720,31 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Aaron Nola</t>
+          <t>Ray Kerr</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>605400</t>
+          <t>678061</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L9" t="n">
-        <v>44.4</v>
+        <v>48.6</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -2730,65 +2758,61 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Strong Barrel, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P9" t="n">
-        <v>34.7</v>
+        <v>49</v>
       </c>
       <c r="Q9" t="n">
-        <v>47.8</v>
+        <v>20</v>
       </c>
       <c r="R9" t="n">
-        <v>30.9</v>
+        <v>52.9</v>
       </c>
       <c r="S9" t="n">
-        <v>59.8</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="T9" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U9" t="n">
-        <v>24</v>
+        <v>32.5</v>
       </c>
       <c r="V9" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X9" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr"/>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026/2025 P:2026</t>
         </is>
       </c>
       <c r="AD9" t="inlineStr"/>
@@ -2805,12 +2829,12 @@
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>28</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
@@ -2820,12 +2844,12 @@
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>Last 7 games: 3/19, 1 HR</t>
+          <t>Last 7 games: 6/28, 1 HR</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 9.2% barrel, 31.3 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 5.9% barrel, 2.0 HR allowed</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
@@ -2835,101 +2859,109 @@
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>7.31</t>
+          <t>10.9</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>42.88</t>
+          <t>44.21</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>90.52</t>
+          <t>90.39</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>99.7248</t>
+          <t>101.6293</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>0.3833</t>
+          <t>0.4843</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
         <is>
-          <t>0.1477</t>
+          <t>0.2142</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>0.315</t>
+          <t>0.3757</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
         <is>
-          <t>71.24</t>
+          <t>74.1</t>
         </is>
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>8.65</t>
+          <t>45.01</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>43.03</t>
+          <t>38.47</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>30.91</t>
+          <t>26.82</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>13.5</t>
+          <t>28.4</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>0.1602</t>
+          <t>0.219</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>9.24</t>
+          <t>5.9</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>41.2</t>
+          <t>31.4</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>88.77</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>0.4184</t>
+          <t>0.357</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
-          <t>0.1745</t>
+          <t>0.119</t>
         </is>
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>27.39</t>
-        </is>
-      </c>
-      <c r="BG9" t="inlineStr"/>
-      <c r="BH9" t="inlineStr"/>
+          <t>19.6</t>
+        </is>
+      </c>
+      <c r="BG9" t="inlineStr">
+        <is>
+          <t>L To R</t>
+        </is>
+      </c>
+      <c r="BH9" t="inlineStr">
+        <is>
+          <t>79</t>
+        </is>
+      </c>
       <c r="BI9" t="inlineStr">
         <is>
           <t>Truist Park</t>
@@ -2968,12 +3000,12 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -2992,7 +3024,7 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>39.3</v>
+        <v>44.4</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
@@ -3006,7 +3038,7 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P10" t="n">
@@ -3016,10 +3048,10 @@
         <v>20</v>
       </c>
       <c r="R10" t="n">
-        <v>30.9</v>
+        <v>52.9</v>
       </c>
       <c r="S10" t="n">
-        <v>81.90000000000001</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="T10" t="n">
         <v>78</v>
@@ -3029,39 +3061,35 @@
       </c>
       <c r="V10" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X10" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr"/>
       <c r="AC10" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026</t>
@@ -3204,8 +3232,16 @@
           <t>19.6</t>
         </is>
       </c>
-      <c r="BG10" t="inlineStr"/>
-      <c r="BH10" t="inlineStr"/>
+      <c r="BG10" t="inlineStr">
+        <is>
+          <t>L To R</t>
+        </is>
+      </c>
+      <c r="BH10" t="inlineStr">
+        <is>
+          <t>79</t>
+        </is>
+      </c>
       <c r="BI10" t="inlineStr">
         <is>
           <t>Truist Park</t>
@@ -3244,7 +3280,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -3268,7 +3304,7 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>38.7</v>
+        <v>42.6</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -3282,7 +3318,7 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P11" t="n">
@@ -3292,10 +3328,10 @@
         <v>20</v>
       </c>
       <c r="R11" t="n">
-        <v>30.9</v>
+        <v>52.9</v>
       </c>
       <c r="S11" t="n">
-        <v>88.7</v>
+        <v>93.2</v>
       </c>
       <c r="T11" t="n">
         <v>78</v>
@@ -3305,39 +3341,35 @@
       </c>
       <c r="V11" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr"/>
       <c r="AC11" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026</t>
@@ -3480,8 +3512,16 @@
           <t>19.6</t>
         </is>
       </c>
-      <c r="BG11" t="inlineStr"/>
-      <c r="BH11" t="inlineStr"/>
+      <c r="BG11" t="inlineStr">
+        <is>
+          <t>L To R</t>
+        </is>
+      </c>
+      <c r="BH11" t="inlineStr">
+        <is>
+          <t>79</t>
+        </is>
+      </c>
       <c r="BI11" t="inlineStr">
         <is>
           <t>Truist Park</t>
@@ -3520,7 +3560,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -3544,7 +3584,7 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>38.4</v>
+        <v>42.3</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
@@ -3558,7 +3598,7 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge, Hot Hitter/Streak</t>
+          <t>Platoon Edge, Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P12" t="n">
@@ -3568,10 +3608,10 @@
         <v>20</v>
       </c>
       <c r="R12" t="n">
-        <v>30.9</v>
+        <v>52.9</v>
       </c>
       <c r="S12" t="n">
-        <v>59.8</v>
+        <v>64.3</v>
       </c>
       <c r="T12" t="n">
         <v>78</v>
@@ -3581,39 +3621,35 @@
       </c>
       <c r="V12" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W12" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X12" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="Y12" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr"/>
       <c r="AC12" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026</t>
@@ -3756,8 +3792,16 @@
           <t>19.6</t>
         </is>
       </c>
-      <c r="BG12" t="inlineStr"/>
-      <c r="BH12" t="inlineStr"/>
+      <c r="BG12" t="inlineStr">
+        <is>
+          <t>L To R</t>
+        </is>
+      </c>
+      <c r="BH12" t="inlineStr">
+        <is>
+          <t>79</t>
+        </is>
+      </c>
       <c r="BI12" t="inlineStr">
         <is>
           <t>Truist Park</t>
@@ -3776,7 +3820,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Mauricio Dubon</t>
+          <t>Mauricio Dubón</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -3796,7 +3840,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -3820,7 +3864,7 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>38</v>
+        <v>41.9</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
@@ -3834,7 +3878,7 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>No major boost</t>
         </is>
       </c>
       <c r="P13" t="n">
@@ -3844,10 +3888,10 @@
         <v>47.8</v>
       </c>
       <c r="R13" t="n">
-        <v>30.9</v>
+        <v>52.9</v>
       </c>
       <c r="S13" t="n">
-        <v>81.90000000000001</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="T13" t="n">
         <v>50</v>
@@ -3857,39 +3901,35 @@
       </c>
       <c r="V13" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W13" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X13" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Y13" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr"/>
       <c r="AC13" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -4032,8 +4072,16 @@
           <t>27.39</t>
         </is>
       </c>
-      <c r="BG13" t="inlineStr"/>
-      <c r="BH13" t="inlineStr"/>
+      <c r="BG13" t="inlineStr">
+        <is>
+          <t>L To R</t>
+        </is>
+      </c>
+      <c r="BH13" t="inlineStr">
+        <is>
+          <t>79</t>
+        </is>
+      </c>
       <c r="BI13" t="inlineStr">
         <is>
           <t>Truist Park</t>
@@ -4047,12 +4095,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>645277</t>
+          <t>642086</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Ozzie Albies</t>
+          <t>Dominic Smith</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -4072,12 +4120,12 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -4096,7 +4144,7 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>37.8</v>
+        <v>41</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
@@ -4110,62 +4158,58 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P14" t="n">
-        <v>15.3</v>
+        <v>21.8</v>
       </c>
       <c r="Q14" t="n">
-        <v>47.3</v>
+        <v>47.8</v>
       </c>
       <c r="R14" t="n">
-        <v>30.9</v>
+        <v>52.9</v>
       </c>
       <c r="S14" t="n">
-        <v>71.7</v>
+        <v>44.8</v>
       </c>
       <c r="T14" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>18.3</v>
       </c>
       <c r="V14" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W14" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X14" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="Y14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr"/>
       <c r="AC14" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -4185,27 +4229,27 @@
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>11</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>Last 7 games: 3/25, 0 HR</t>
+          <t>Last 7 games: 1/11, 1 HR</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 9.2% barrel, 31.3 HR allowed</t>
+          <t>platoon edge; pitcher baseline 9.2% barrel, 31.3 HR allowed</t>
         </is>
       </c>
       <c r="AM14" t="inlineStr">
@@ -4215,67 +4259,67 @@
       </c>
       <c r="AN14" t="inlineStr">
         <is>
-          <t>4.13</t>
+          <t>5.32</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>28.6</t>
+          <t>33.47</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>87.22</t>
+          <t>87.77</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>96.687</t>
+          <t>97.8111</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>0.346</t>
+          <t>0.384</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
         <is>
-          <t>0.1184</t>
+          <t>0.1401</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>0.2808</t>
+          <t>0.3025</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
         <is>
-          <t>68.86</t>
+          <t>68.5</t>
         </is>
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>5.67</t>
+          <t>5.92</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>46.7</t>
+          <t>37.21</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>31.48</t>
+          <t>28.68</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>20.2</t>
+          <t>7.8</t>
         </is>
       </c>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>0.146</t>
+          <t>0.1309</t>
         </is>
       </c>
       <c r="BA14" t="inlineStr">
@@ -4308,8 +4352,16 @@
           <t>27.39</t>
         </is>
       </c>
-      <c r="BG14" t="inlineStr"/>
-      <c r="BH14" t="inlineStr"/>
+      <c r="BG14" t="inlineStr">
+        <is>
+          <t>L To R</t>
+        </is>
+      </c>
+      <c r="BH14" t="inlineStr">
+        <is>
+          <t>79</t>
+        </is>
+      </c>
       <c r="BI14" t="inlineStr">
         <is>
           <t>Truist Park</t>
@@ -4323,12 +4375,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>669016</t>
+          <t>681082</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Brandon Marsh</t>
+          <t>Bryson Stott</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -4348,12 +4400,12 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -4372,7 +4424,7 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>37.7</v>
+        <v>39.7</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
@@ -4386,62 +4438,58 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>No major boost</t>
         </is>
       </c>
       <c r="P15" t="n">
-        <v>36.1</v>
+        <v>25.2</v>
       </c>
       <c r="Q15" t="n">
         <v>20</v>
       </c>
       <c r="R15" t="n">
-        <v>30.9</v>
+        <v>52.9</v>
       </c>
       <c r="S15" t="n">
-        <v>71.7</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="T15" t="n">
         <v>50</v>
       </c>
       <c r="U15" t="n">
-        <v>35.6</v>
+        <v>40.7</v>
       </c>
       <c r="V15" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W15" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X15" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="Y15" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr"/>
       <c r="AC15" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026</t>
@@ -4461,22 +4509,22 @@
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>23</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/17, 1 HR</t>
+          <t>Contact streak: 9/23 over last 7 games</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
@@ -4491,67 +4539,67 @@
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>8.12</t>
+          <t>5.66</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>43.74</t>
+          <t>35.24</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>89.77</t>
+          <t>88.86</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>100.0232</t>
+          <t>98.4048</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>0.4103</t>
+          <t>0.3993</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
         <is>
-          <t>0.1564</t>
+          <t>0.1383</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>0.3097</t>
+          <t>0.3249</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
         <is>
-          <t>71.54</t>
+          <t>69.72</t>
         </is>
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>15.58</t>
+          <t>6.75</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>38.26</t>
+          <t>34.17</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>26.87</t>
+          <t>27.59</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>15.9</t>
+          <t>10.9</t>
         </is>
       </c>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>0.1525</t>
+          <t>0.1417</t>
         </is>
       </c>
       <c r="BA15" t="inlineStr">
@@ -4584,8 +4632,16 @@
           <t>19.6</t>
         </is>
       </c>
-      <c r="BG15" t="inlineStr"/>
-      <c r="BH15" t="inlineStr"/>
+      <c r="BG15" t="inlineStr">
+        <is>
+          <t>L To R</t>
+        </is>
+      </c>
+      <c r="BH15" t="inlineStr">
+        <is>
+          <t>79</t>
+        </is>
+      </c>
       <c r="BI15" t="inlineStr">
         <is>
           <t>Truist Park</t>
@@ -4599,24 +4655,24 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>669221</t>
+          <t>650559</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Sean Murphy</t>
+          <t>Bryan De La Cruz</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
+          <t>PHI</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
           <t>ATL</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>PHI</t>
-        </is>
-      </c>
       <c r="F16" t="inlineStr">
         <is>
           <t>2026-10-02T00:00:00Z</t>
@@ -4624,31 +4680,31 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Aaron Nola</t>
+          <t>Ray Kerr</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>605400</t>
+          <t>678061</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L16" t="n">
-        <v>37.6</v>
+        <v>38.6</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
@@ -4662,65 +4718,61 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P16" t="n">
-        <v>34</v>
+        <v>24.8</v>
       </c>
       <c r="Q16" t="n">
-        <v>47.8</v>
+        <v>20</v>
       </c>
       <c r="R16" t="n">
-        <v>30.9</v>
+        <v>52.9</v>
       </c>
       <c r="S16" t="n">
-        <v>40.2</v>
+        <v>76.2</v>
       </c>
       <c r="T16" t="n">
-        <v>50</v>
+        <v>78</v>
       </c>
       <c r="U16" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="V16" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W16" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X16" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="Y16" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr"/>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026/2025 P:2026</t>
         </is>
       </c>
       <c r="AD16" t="inlineStr"/>
@@ -4737,12 +4789,12 @@
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>17</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
@@ -4752,12 +4804,12 @@
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>Last 7 games: 3/21, 0 HR</t>
+          <t>Last 7 games: 2/17, 0 HR</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 9.2% barrel, 31.3 HR allowed</t>
+          <t>platoon edge; pitcher baseline 5.9% barrel, 2.0 HR allowed</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
@@ -4767,101 +4819,109 @@
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>9.76</t>
+          <t>5.64</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>41.7</t>
+          <t>44.0</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>88.19</t>
+          <t>89.61</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>101.2803</t>
+          <t>99.8033</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>0.3548</t>
+          <t>0.3346</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
         <is>
-          <t>0.151</t>
+          <t>0.1063</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>0.2853</t>
+          <t>0.2828</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
         <is>
-          <t>72.6</t>
+          <t>70.92</t>
         </is>
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>29.59</t>
+          <t>16.37</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>49.12</t>
+          <t>38.67</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>25.37</t>
+          <t>19.87</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>6.9</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>0.1456</t>
+          <t>0.0997</t>
         </is>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>9.24</t>
+          <t>5.9</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>41.2</t>
+          <t>31.4</t>
         </is>
       </c>
       <c r="BC16" t="inlineStr">
         <is>
-          <t>88.77</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="BD16" t="inlineStr">
         <is>
-          <t>0.4184</t>
+          <t>0.357</t>
         </is>
       </c>
       <c r="BE16" t="inlineStr">
         <is>
-          <t>0.1745</t>
+          <t>0.119</t>
         </is>
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>27.39</t>
-        </is>
-      </c>
-      <c r="BG16" t="inlineStr"/>
-      <c r="BH16" t="inlineStr"/>
+          <t>19.6</t>
+        </is>
+      </c>
+      <c r="BG16" t="inlineStr">
+        <is>
+          <t>L To R</t>
+        </is>
+      </c>
+      <c r="BH16" t="inlineStr">
+        <is>
+          <t>79</t>
+        </is>
+      </c>
       <c r="BI16" t="inlineStr">
         <is>
           <t>Truist Park</t>
@@ -4875,24 +4935,24 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>681082</t>
+          <t>645277</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Bryson Stott</t>
+          <t>Ozzie Albies</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
+          <t>ATL</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
           <t>PHI</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>ATL</t>
-        </is>
-      </c>
       <c r="F17" t="inlineStr">
         <is>
           <t>2026-10-02T00:00:00Z</t>
@@ -4900,31 +4960,31 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Ray Kerr</t>
+          <t>Aaron Nola</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>678061</t>
+          <t>605400</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L17" t="n">
-        <v>36.9</v>
+        <v>38.4</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
@@ -4938,65 +4998,61 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P17" t="n">
-        <v>25.2</v>
+        <v>15.3</v>
       </c>
       <c r="Q17" t="n">
-        <v>20</v>
+        <v>47.3</v>
       </c>
       <c r="R17" t="n">
-        <v>30.9</v>
+        <v>52.9</v>
       </c>
       <c r="S17" t="n">
-        <v>90.40000000000001</v>
+        <v>52.4</v>
       </c>
       <c r="T17" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="U17" t="n">
-        <v>40.7</v>
+        <v>0</v>
       </c>
       <c r="V17" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W17" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X17" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Y17" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr"/>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD17" t="inlineStr"/>
@@ -5013,12 +5069,12 @@
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
@@ -5028,12 +5084,12 @@
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>Contact streak: 9/23 over last 7 games</t>
+          <t>Last 7 games: 3/25, 0 HR</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 5.9% barrel, 2.0 HR allowed</t>
+          <t>switch hitter; pitcher baseline 9.2% barrel, 31.3 HR allowed</t>
         </is>
       </c>
       <c r="AM17" t="inlineStr">
@@ -5043,101 +5099,109 @@
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>5.66</t>
+          <t>4.13</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>35.24</t>
+          <t>28.6</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>88.86</t>
+          <t>87.22</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>98.4048</t>
+          <t>96.687</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>0.3993</t>
+          <t>0.346</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
         <is>
-          <t>0.1383</t>
+          <t>0.1184</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>0.3249</t>
+          <t>0.2808</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
         <is>
-          <t>69.72</t>
+          <t>68.86</t>
         </is>
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>6.75</t>
+          <t>5.67</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>34.17</t>
+          <t>46.7</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>27.59</t>
+          <t>31.48</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>10.9</t>
+          <t>20.2</t>
         </is>
       </c>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>0.1417</t>
+          <t>0.146</t>
         </is>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>5.9</t>
+          <t>9.24</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>31.4</t>
+          <t>41.2</t>
         </is>
       </c>
       <c r="BC17" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>88.77</t>
         </is>
       </c>
       <c r="BD17" t="inlineStr">
         <is>
-          <t>0.357</t>
+          <t>0.4184</t>
         </is>
       </c>
       <c r="BE17" t="inlineStr">
         <is>
-          <t>0.119</t>
+          <t>0.1745</t>
         </is>
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>19.6</t>
-        </is>
-      </c>
-      <c r="BG17" t="inlineStr"/>
-      <c r="BH17" t="inlineStr"/>
+          <t>27.39</t>
+        </is>
+      </c>
+      <c r="BG17" t="inlineStr">
+        <is>
+          <t>L To R</t>
+        </is>
+      </c>
+      <c r="BH17" t="inlineStr">
+        <is>
+          <t>79</t>
+        </is>
+      </c>
       <c r="BI17" t="inlineStr">
         <is>
           <t>Truist Park</t>
@@ -5176,12 +5240,12 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -5200,7 +5264,7 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>32.7</v>
+        <v>37.7</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
@@ -5214,7 +5278,7 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P18" t="n">
@@ -5224,10 +5288,10 @@
         <v>20</v>
       </c>
       <c r="R18" t="n">
-        <v>30.9</v>
+        <v>52.9</v>
       </c>
       <c r="S18" t="n">
-        <v>40.2</v>
+        <v>52.4</v>
       </c>
       <c r="T18" t="n">
         <v>78</v>
@@ -5237,39 +5301,35 @@
       </c>
       <c r="V18" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W18" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X18" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="Y18" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr"/>
       <c r="AC18" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026</t>
@@ -5412,8 +5472,16 @@
           <t>19.6</t>
         </is>
       </c>
-      <c r="BG18" t="inlineStr"/>
-      <c r="BH18" t="inlineStr"/>
+      <c r="BG18" t="inlineStr">
+        <is>
+          <t>L To R</t>
+        </is>
+      </c>
+      <c r="BH18" t="inlineStr">
+        <is>
+          <t>79</t>
+        </is>
+      </c>
       <c r="BI18" t="inlineStr">
         <is>
           <t>Truist Park</t>
@@ -5452,12 +5520,12 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -5476,7 +5544,7 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>25.1</v>
+        <v>28</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
@@ -5490,7 +5558,7 @@
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>No major boost</t>
         </is>
       </c>
       <c r="P19" t="n">
@@ -5500,10 +5568,10 @@
         <v>20</v>
       </c>
       <c r="R19" t="n">
-        <v>30.9</v>
+        <v>52.9</v>
       </c>
       <c r="S19" t="n">
-        <v>47.9</v>
+        <v>44.8</v>
       </c>
       <c r="T19" t="n">
         <v>50</v>
@@ -5513,39 +5581,35 @@
       </c>
       <c r="V19" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W19" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X19" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="Y19" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr"/>
       <c r="AC19" t="inlineStr">
         <is>
           <t>H:2026 P:2026</t>
@@ -5688,8 +5752,16 @@
           <t>19.6</t>
         </is>
       </c>
-      <c r="BG19" t="inlineStr"/>
-      <c r="BH19" t="inlineStr"/>
+      <c r="BG19" t="inlineStr">
+        <is>
+          <t>L To R</t>
+        </is>
+      </c>
+      <c r="BH19" t="inlineStr">
+        <is>
+          <t>79</t>
+        </is>
+      </c>
       <c r="BI19" t="inlineStr">
         <is>
           <t>Truist Park</t>
@@ -6054,7 +6126,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -6078,11 +6150,11 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>59</v>
+        <v>62.9</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>Longshot</t>
+          <t>Tier 3</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -6092,7 +6164,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P2" t="n">
@@ -6102,10 +6174,10 @@
         <v>47.8</v>
       </c>
       <c r="R2" t="n">
-        <v>30.9</v>
+        <v>52.9</v>
       </c>
       <c r="S2" t="n">
-        <v>92.09999999999999</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="T2" t="n">
         <v>80</v>
@@ -6115,39 +6187,35 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr"/>
       <c r="AC2" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -6290,8 +6358,16 @@
           <t>27.39</t>
         </is>
       </c>
-      <c r="BG2" t="inlineStr"/>
-      <c r="BH2" t="inlineStr"/>
+      <c r="BG2" t="inlineStr">
+        <is>
+          <t>L To R</t>
+        </is>
+      </c>
+      <c r="BH2" t="inlineStr">
+        <is>
+          <t>79</t>
+        </is>
+      </c>
       <c r="BI2" t="inlineStr">
         <is>
           <t>Truist Park</t>
@@ -6330,12 +6406,12 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -6354,11 +6430,11 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>57.4</v>
+        <v>61.1</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>Longshot</t>
+          <t>Tier 3</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -6368,7 +6444,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P3" t="n">
@@ -6378,10 +6454,10 @@
         <v>47.8</v>
       </c>
       <c r="R3" t="n">
-        <v>30.9</v>
+        <v>52.9</v>
       </c>
       <c r="S3" t="n">
-        <v>90.40000000000001</v>
+        <v>93.2</v>
       </c>
       <c r="T3" t="n">
         <v>80</v>
@@ -6391,39 +6467,35 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr"/>
       <c r="AC3" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -6566,8 +6638,16 @@
           <t>27.39</t>
         </is>
       </c>
-      <c r="BG3" t="inlineStr"/>
-      <c r="BH3" t="inlineStr"/>
+      <c r="BG3" t="inlineStr">
+        <is>
+          <t>L To R</t>
+        </is>
+      </c>
+      <c r="BH3" t="inlineStr">
+        <is>
+          <t>79</t>
+        </is>
+      </c>
       <c r="BI3" t="inlineStr">
         <is>
           <t>Truist Park</t>
@@ -6586,7 +6666,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Ronald Acuna</t>
+          <t>Ronald Acuña Jr.</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -6606,7 +6686,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -6630,7 +6710,7 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
@@ -6644,7 +6724,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot</t>
+          <t>Strong Barrel, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P4" t="n">
@@ -6654,10 +6734,10 @@
         <v>47.8</v>
       </c>
       <c r="R4" t="n">
-        <v>30.9</v>
+        <v>52.9</v>
       </c>
       <c r="S4" t="n">
-        <v>95.5</v>
+        <v>100</v>
       </c>
       <c r="T4" t="n">
         <v>50</v>
@@ -6667,39 +6747,35 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr"/>
       <c r="AC4" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -6842,8 +6918,16 @@
           <t>27.39</t>
         </is>
       </c>
-      <c r="BG4" t="inlineStr"/>
-      <c r="BH4" t="inlineStr"/>
+      <c r="BG4" t="inlineStr">
+        <is>
+          <t>L To R</t>
+        </is>
+      </c>
+      <c r="BH4" t="inlineStr">
+        <is>
+          <t>79</t>
+        </is>
+      </c>
       <c r="BI4" t="inlineStr">
         <is>
           <t>Truist Park</t>
@@ -6862,7 +6946,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Michael Harris</t>
+          <t>Michael Harris II</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -6882,12 +6966,12 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -6906,7 +6990,7 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>52.2</v>
+        <v>56.4</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -6920,7 +7004,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P5" t="n">
@@ -6930,10 +7014,10 @@
         <v>47.8</v>
       </c>
       <c r="R5" t="n">
-        <v>30.9</v>
+        <v>52.9</v>
       </c>
       <c r="S5" t="n">
-        <v>88.7</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="T5" t="n">
         <v>80</v>
@@ -6943,39 +7027,35 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr"/>
       <c r="AC5" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -7118,8 +7198,16 @@
           <t>27.39</t>
         </is>
       </c>
-      <c r="BG5" t="inlineStr"/>
-      <c r="BH5" t="inlineStr"/>
+      <c r="BG5" t="inlineStr">
+        <is>
+          <t>L To R</t>
+        </is>
+      </c>
+      <c r="BH5" t="inlineStr">
+        <is>
+          <t>79</t>
+        </is>
+      </c>
       <c r="BI5" t="inlineStr">
         <is>
           <t>Truist Park</t>
@@ -7158,7 +7246,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -7182,7 +7270,7 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>51.9</v>
+        <v>55.8</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -7196,7 +7284,7 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot</t>
+          <t>Strong Barrel, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P6" t="n">
@@ -7206,10 +7294,10 @@
         <v>20</v>
       </c>
       <c r="R6" t="n">
-        <v>30.9</v>
+        <v>52.9</v>
       </c>
       <c r="S6" t="n">
-        <v>95.5</v>
+        <v>100</v>
       </c>
       <c r="T6" t="n">
         <v>50</v>
@@ -7219,39 +7307,35 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr"/>
       <c r="AC6" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026</t>
@@ -7394,8 +7478,16 @@
           <t>19.6</t>
         </is>
       </c>
-      <c r="BG6" t="inlineStr"/>
-      <c r="BH6" t="inlineStr"/>
+      <c r="BG6" t="inlineStr">
+        <is>
+          <t>L To R</t>
+        </is>
+      </c>
+      <c r="BH6" t="inlineStr">
+        <is>
+          <t>79</t>
+        </is>
+      </c>
       <c r="BI6" t="inlineStr">
         <is>
           <t>Truist Park</t>
@@ -7434,12 +7526,12 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -7458,7 +7550,7 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>47.4</v>
+        <v>53</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -7472,7 +7564,7 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel</t>
+          <t>Strong Barrel</t>
         </is>
       </c>
       <c r="P7" t="n">
@@ -7482,10 +7574,10 @@
         <v>47.8</v>
       </c>
       <c r="R7" t="n">
-        <v>30.9</v>
+        <v>52.9</v>
       </c>
       <c r="S7" t="n">
-        <v>47.9</v>
+        <v>64.3</v>
       </c>
       <c r="T7" t="n">
         <v>50</v>
@@ -7495,39 +7587,35 @@
       </c>
       <c r="V7" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr"/>
       <c r="AC7" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -7670,8 +7758,16 @@
           <t>27.39</t>
         </is>
       </c>
-      <c r="BG7" t="inlineStr"/>
-      <c r="BH7" t="inlineStr"/>
+      <c r="BG7" t="inlineStr">
+        <is>
+          <t>L To R</t>
+        </is>
+      </c>
+      <c r="BH7" t="inlineStr">
+        <is>
+          <t>79</t>
+        </is>
+      </c>
       <c r="BI7" t="inlineStr">
         <is>
           <t>Truist Park</t>
@@ -7685,24 +7781,24 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>547180</t>
+          <t>573262</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Bryce Harper</t>
+          <t>Mike Yastrzemski</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
+          <t>ATL</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
           <t>PHI</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>ATL</t>
-        </is>
-      </c>
       <c r="F8" t="inlineStr">
         <is>
           <t>2026-10-02T00:00:00Z</t>
@@ -7710,31 +7806,31 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Ray Kerr</t>
+          <t>Aaron Nola</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>678061</t>
+          <t>605400</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L8" t="n">
-        <v>44.6</v>
+        <v>49.9</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -7748,65 +7844,61 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P8" t="n">
-        <v>49</v>
+        <v>34.7</v>
       </c>
       <c r="Q8" t="n">
-        <v>20</v>
+        <v>47.8</v>
       </c>
       <c r="R8" t="n">
-        <v>30.9</v>
+        <v>52.9</v>
       </c>
       <c r="S8" t="n">
-        <v>92.09999999999999</v>
+        <v>76.2</v>
       </c>
       <c r="T8" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U8" t="n">
-        <v>32.5</v>
+        <v>24</v>
       </c>
       <c r="V8" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr"/>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD8" t="inlineStr"/>
@@ -7823,12 +7915,12 @@
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>19</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
@@ -7838,12 +7930,12 @@
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/28, 1 HR</t>
+          <t>Last 7 games: 3/19, 1 HR</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 5.9% barrel, 2.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 9.2% barrel, 31.3 HR allowed</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
@@ -7853,101 +7945,109 @@
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>10.9</t>
+          <t>7.31</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>44.21</t>
+          <t>42.88</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>90.39</t>
+          <t>90.52</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>101.6293</t>
+          <t>99.7248</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>0.4843</t>
+          <t>0.3833</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
-          <t>0.2142</t>
+          <t>0.1477</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>0.3757</t>
+          <t>0.315</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
         <is>
-          <t>74.1</t>
+          <t>71.24</t>
         </is>
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>45.01</t>
+          <t>8.65</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>38.47</t>
+          <t>43.03</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>26.82</t>
+          <t>30.91</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>28.4</t>
+          <t>13.5</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>0.219</t>
+          <t>0.1602</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>5.9</t>
+          <t>9.24</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>31.4</t>
+          <t>41.2</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>88.77</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>0.357</t>
+          <t>0.4184</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
-          <t>0.119</t>
+          <t>0.1745</t>
         </is>
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>19.6</t>
-        </is>
-      </c>
-      <c r="BG8" t="inlineStr"/>
-      <c r="BH8" t="inlineStr"/>
+          <t>27.39</t>
+        </is>
+      </c>
+      <c r="BG8" t="inlineStr">
+        <is>
+          <t>L To R</t>
+        </is>
+      </c>
+      <c r="BH8" t="inlineStr">
+        <is>
+          <t>79</t>
+        </is>
+      </c>
       <c r="BI8" t="inlineStr">
         <is>
           <t>Truist Park</t>
@@ -7961,24 +8061,24 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>573262</t>
+          <t>547180</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Mike Yastrzemski</t>
+          <t>Bryce Harper</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
+          <t>PHI</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
           <t>ATL</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>PHI</t>
-        </is>
-      </c>
       <c r="F9" t="inlineStr">
         <is>
           <t>2026-10-02T00:00:00Z</t>
@@ -7986,31 +8086,31 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Aaron Nola</t>
+          <t>Ray Kerr</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>605400</t>
+          <t>678061</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L9" t="n">
-        <v>44.4</v>
+        <v>48.6</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -8024,65 +8124,61 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Strong Barrel, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P9" t="n">
-        <v>34.7</v>
+        <v>49</v>
       </c>
       <c r="Q9" t="n">
-        <v>47.8</v>
+        <v>20</v>
       </c>
       <c r="R9" t="n">
-        <v>30.9</v>
+        <v>52.9</v>
       </c>
       <c r="S9" t="n">
-        <v>59.8</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="T9" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U9" t="n">
-        <v>24</v>
+        <v>32.5</v>
       </c>
       <c r="V9" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X9" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr"/>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026/2025 P:2026</t>
         </is>
       </c>
       <c r="AD9" t="inlineStr"/>
@@ -8099,12 +8195,12 @@
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>28</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
@@ -8114,12 +8210,12 @@
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>Last 7 games: 3/19, 1 HR</t>
+          <t>Last 7 games: 6/28, 1 HR</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 9.2% barrel, 31.3 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 5.9% barrel, 2.0 HR allowed</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
@@ -8129,101 +8225,109 @@
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>7.31</t>
+          <t>10.9</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>42.88</t>
+          <t>44.21</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>90.52</t>
+          <t>90.39</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>99.7248</t>
+          <t>101.6293</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>0.3833</t>
+          <t>0.4843</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
         <is>
-          <t>0.1477</t>
+          <t>0.2142</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>0.315</t>
+          <t>0.3757</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
         <is>
-          <t>71.24</t>
+          <t>74.1</t>
         </is>
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>8.65</t>
+          <t>45.01</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>43.03</t>
+          <t>38.47</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>30.91</t>
+          <t>26.82</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>13.5</t>
+          <t>28.4</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>0.1602</t>
+          <t>0.219</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>9.24</t>
+          <t>5.9</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>41.2</t>
+          <t>31.4</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>88.77</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>0.4184</t>
+          <t>0.357</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
-          <t>0.1745</t>
+          <t>0.119</t>
         </is>
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>27.39</t>
-        </is>
-      </c>
-      <c r="BG9" t="inlineStr"/>
-      <c r="BH9" t="inlineStr"/>
+          <t>19.6</t>
+        </is>
+      </c>
+      <c r="BG9" t="inlineStr">
+        <is>
+          <t>L To R</t>
+        </is>
+      </c>
+      <c r="BH9" t="inlineStr">
+        <is>
+          <t>79</t>
+        </is>
+      </c>
       <c r="BI9" t="inlineStr">
         <is>
           <t>Truist Park</t>
@@ -8262,12 +8366,12 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -8286,7 +8390,7 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>39.3</v>
+        <v>44.4</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
@@ -8300,7 +8404,7 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P10" t="n">
@@ -8310,10 +8414,10 @@
         <v>20</v>
       </c>
       <c r="R10" t="n">
-        <v>30.9</v>
+        <v>52.9</v>
       </c>
       <c r="S10" t="n">
-        <v>81.90000000000001</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="T10" t="n">
         <v>78</v>
@@ -8323,39 +8427,35 @@
       </c>
       <c r="V10" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X10" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr"/>
       <c r="AC10" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026</t>
@@ -8498,8 +8598,16 @@
           <t>19.6</t>
         </is>
       </c>
-      <c r="BG10" t="inlineStr"/>
-      <c r="BH10" t="inlineStr"/>
+      <c r="BG10" t="inlineStr">
+        <is>
+          <t>L To R</t>
+        </is>
+      </c>
+      <c r="BH10" t="inlineStr">
+        <is>
+          <t>79</t>
+        </is>
+      </c>
       <c r="BI10" t="inlineStr">
         <is>
           <t>Truist Park</t>
@@ -8538,7 +8646,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -8562,7 +8670,7 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>38.7</v>
+        <v>42.6</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -8576,7 +8684,7 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P11" t="n">
@@ -8586,10 +8694,10 @@
         <v>20</v>
       </c>
       <c r="R11" t="n">
-        <v>30.9</v>
+        <v>52.9</v>
       </c>
       <c r="S11" t="n">
-        <v>88.7</v>
+        <v>93.2</v>
       </c>
       <c r="T11" t="n">
         <v>78</v>
@@ -8599,39 +8707,35 @@
       </c>
       <c r="V11" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr"/>
       <c r="AC11" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026</t>
@@ -8774,8 +8878,16 @@
           <t>19.6</t>
         </is>
       </c>
-      <c r="BG11" t="inlineStr"/>
-      <c r="BH11" t="inlineStr"/>
+      <c r="BG11" t="inlineStr">
+        <is>
+          <t>L To R</t>
+        </is>
+      </c>
+      <c r="BH11" t="inlineStr">
+        <is>
+          <t>79</t>
+        </is>
+      </c>
       <c r="BI11" t="inlineStr">
         <is>
           <t>Truist Park</t>
@@ -8814,7 +8926,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -8838,7 +8950,7 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>38.4</v>
+        <v>42.3</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
@@ -8852,7 +8964,7 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge, Hot Hitter/Streak</t>
+          <t>Platoon Edge, Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P12" t="n">
@@ -8862,10 +8974,10 @@
         <v>20</v>
       </c>
       <c r="R12" t="n">
-        <v>30.9</v>
+        <v>52.9</v>
       </c>
       <c r="S12" t="n">
-        <v>59.8</v>
+        <v>64.3</v>
       </c>
       <c r="T12" t="n">
         <v>78</v>
@@ -8875,39 +8987,35 @@
       </c>
       <c r="V12" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W12" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X12" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="Y12" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr"/>
       <c r="AC12" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026</t>
@@ -9050,8 +9158,16 @@
           <t>19.6</t>
         </is>
       </c>
-      <c r="BG12" t="inlineStr"/>
-      <c r="BH12" t="inlineStr"/>
+      <c r="BG12" t="inlineStr">
+        <is>
+          <t>L To R</t>
+        </is>
+      </c>
+      <c r="BH12" t="inlineStr">
+        <is>
+          <t>79</t>
+        </is>
+      </c>
       <c r="BI12" t="inlineStr">
         <is>
           <t>Truist Park</t>
@@ -9070,7 +9186,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Mauricio Dubon</t>
+          <t>Mauricio Dubón</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -9090,7 +9206,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -9114,7 +9230,7 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>38</v>
+        <v>41.9</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
@@ -9128,7 +9244,7 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>No major boost</t>
         </is>
       </c>
       <c r="P13" t="n">
@@ -9138,10 +9254,10 @@
         <v>47.8</v>
       </c>
       <c r="R13" t="n">
-        <v>30.9</v>
+        <v>52.9</v>
       </c>
       <c r="S13" t="n">
-        <v>81.90000000000001</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="T13" t="n">
         <v>50</v>
@@ -9151,39 +9267,35 @@
       </c>
       <c r="V13" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W13" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X13" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Y13" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr"/>
       <c r="AC13" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -9326,8 +9438,16 @@
           <t>27.39</t>
         </is>
       </c>
-      <c r="BG13" t="inlineStr"/>
-      <c r="BH13" t="inlineStr"/>
+      <c r="BG13" t="inlineStr">
+        <is>
+          <t>L To R</t>
+        </is>
+      </c>
+      <c r="BH13" t="inlineStr">
+        <is>
+          <t>79</t>
+        </is>
+      </c>
       <c r="BI13" t="inlineStr">
         <is>
           <t>Truist Park</t>
@@ -9341,12 +9461,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>645277</t>
+          <t>642086</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Ozzie Albies</t>
+          <t>Dominic Smith</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -9366,12 +9486,12 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -9390,7 +9510,7 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>37.8</v>
+        <v>41</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
@@ -9404,62 +9524,58 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P14" t="n">
-        <v>15.3</v>
+        <v>21.8</v>
       </c>
       <c r="Q14" t="n">
-        <v>47.3</v>
+        <v>47.8</v>
       </c>
       <c r="R14" t="n">
-        <v>30.9</v>
+        <v>52.9</v>
       </c>
       <c r="S14" t="n">
-        <v>71.7</v>
+        <v>44.8</v>
       </c>
       <c r="T14" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>18.3</v>
       </c>
       <c r="V14" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W14" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X14" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="Y14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr"/>
       <c r="AC14" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -9479,27 +9595,27 @@
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>11</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>Last 7 games: 3/25, 0 HR</t>
+          <t>Last 7 games: 1/11, 1 HR</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 9.2% barrel, 31.3 HR allowed</t>
+          <t>platoon edge; pitcher baseline 9.2% barrel, 31.3 HR allowed</t>
         </is>
       </c>
       <c r="AM14" t="inlineStr">
@@ -9509,67 +9625,67 @@
       </c>
       <c r="AN14" t="inlineStr">
         <is>
-          <t>4.13</t>
+          <t>5.32</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>28.6</t>
+          <t>33.47</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>87.22</t>
+          <t>87.77</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>96.687</t>
+          <t>97.8111</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>0.346</t>
+          <t>0.384</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
         <is>
-          <t>0.1184</t>
+          <t>0.1401</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>0.2808</t>
+          <t>0.3025</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
         <is>
-          <t>68.86</t>
+          <t>68.5</t>
         </is>
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>5.67</t>
+          <t>5.92</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>46.7</t>
+          <t>37.21</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>31.48</t>
+          <t>28.68</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>20.2</t>
+          <t>7.8</t>
         </is>
       </c>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>0.146</t>
+          <t>0.1309</t>
         </is>
       </c>
       <c r="BA14" t="inlineStr">
@@ -9602,8 +9718,16 @@
           <t>27.39</t>
         </is>
       </c>
-      <c r="BG14" t="inlineStr"/>
-      <c r="BH14" t="inlineStr"/>
+      <c r="BG14" t="inlineStr">
+        <is>
+          <t>L To R</t>
+        </is>
+      </c>
+      <c r="BH14" t="inlineStr">
+        <is>
+          <t>79</t>
+        </is>
+      </c>
       <c r="BI14" t="inlineStr">
         <is>
           <t>Truist Park</t>
@@ -9617,12 +9741,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>669016</t>
+          <t>681082</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Brandon Marsh</t>
+          <t>Bryson Stott</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -9642,12 +9766,12 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -9666,7 +9790,7 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>37.7</v>
+        <v>39.7</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
@@ -9680,62 +9804,58 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>No major boost</t>
         </is>
       </c>
       <c r="P15" t="n">
-        <v>36.1</v>
+        <v>25.2</v>
       </c>
       <c r="Q15" t="n">
         <v>20</v>
       </c>
       <c r="R15" t="n">
-        <v>30.9</v>
+        <v>52.9</v>
       </c>
       <c r="S15" t="n">
-        <v>71.7</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="T15" t="n">
         <v>50</v>
       </c>
       <c r="U15" t="n">
-        <v>35.6</v>
+        <v>40.7</v>
       </c>
       <c r="V15" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W15" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X15" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="Y15" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr"/>
       <c r="AC15" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026</t>
@@ -9755,22 +9875,22 @@
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>23</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/17, 1 HR</t>
+          <t>Contact streak: 9/23 over last 7 games</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
@@ -9785,67 +9905,67 @@
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>8.12</t>
+          <t>5.66</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>43.74</t>
+          <t>35.24</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>89.77</t>
+          <t>88.86</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>100.0232</t>
+          <t>98.4048</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>0.4103</t>
+          <t>0.3993</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
         <is>
-          <t>0.1564</t>
+          <t>0.1383</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>0.3097</t>
+          <t>0.3249</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
         <is>
-          <t>71.54</t>
+          <t>69.72</t>
         </is>
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>15.58</t>
+          <t>6.75</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>38.26</t>
+          <t>34.17</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>26.87</t>
+          <t>27.59</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>15.9</t>
+          <t>10.9</t>
         </is>
       </c>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>0.1525</t>
+          <t>0.1417</t>
         </is>
       </c>
       <c r="BA15" t="inlineStr">
@@ -9878,8 +9998,16 @@
           <t>19.6</t>
         </is>
       </c>
-      <c r="BG15" t="inlineStr"/>
-      <c r="BH15" t="inlineStr"/>
+      <c r="BG15" t="inlineStr">
+        <is>
+          <t>L To R</t>
+        </is>
+      </c>
+      <c r="BH15" t="inlineStr">
+        <is>
+          <t>79</t>
+        </is>
+      </c>
       <c r="BI15" t="inlineStr">
         <is>
           <t>Truist Park</t>
@@ -9893,24 +10021,24 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>669221</t>
+          <t>650559</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Sean Murphy</t>
+          <t>Bryan De La Cruz</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
+          <t>PHI</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
           <t>ATL</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>PHI</t>
-        </is>
-      </c>
       <c r="F16" t="inlineStr">
         <is>
           <t>2026-10-02T00:00:00Z</t>
@@ -9918,31 +10046,31 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Aaron Nola</t>
+          <t>Ray Kerr</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>605400</t>
+          <t>678061</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L16" t="n">
-        <v>37.6</v>
+        <v>38.6</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
@@ -9956,65 +10084,61 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P16" t="n">
-        <v>34</v>
+        <v>24.8</v>
       </c>
       <c r="Q16" t="n">
-        <v>47.8</v>
+        <v>20</v>
       </c>
       <c r="R16" t="n">
-        <v>30.9</v>
+        <v>52.9</v>
       </c>
       <c r="S16" t="n">
-        <v>40.2</v>
+        <v>76.2</v>
       </c>
       <c r="T16" t="n">
-        <v>50</v>
+        <v>78</v>
       </c>
       <c r="U16" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="V16" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W16" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X16" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="Y16" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr"/>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026/2025 P:2026</t>
         </is>
       </c>
       <c r="AD16" t="inlineStr"/>
@@ -10031,12 +10155,12 @@
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>17</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
@@ -10046,12 +10170,12 @@
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>Last 7 games: 3/21, 0 HR</t>
+          <t>Last 7 games: 2/17, 0 HR</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 9.2% barrel, 31.3 HR allowed</t>
+          <t>platoon edge; pitcher baseline 5.9% barrel, 2.0 HR allowed</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
@@ -10061,101 +10185,109 @@
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>9.76</t>
+          <t>5.64</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>41.7</t>
+          <t>44.0</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>88.19</t>
+          <t>89.61</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>101.2803</t>
+          <t>99.8033</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>0.3548</t>
+          <t>0.3346</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
         <is>
-          <t>0.151</t>
+          <t>0.1063</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>0.2853</t>
+          <t>0.2828</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
         <is>
-          <t>72.6</t>
+          <t>70.92</t>
         </is>
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>29.59</t>
+          <t>16.37</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>49.12</t>
+          <t>38.67</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>25.37</t>
+          <t>19.87</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>6.9</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>0.1456</t>
+          <t>0.0997</t>
         </is>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>9.24</t>
+          <t>5.9</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>41.2</t>
+          <t>31.4</t>
         </is>
       </c>
       <c r="BC16" t="inlineStr">
         <is>
-          <t>88.77</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="BD16" t="inlineStr">
         <is>
-          <t>0.4184</t>
+          <t>0.357</t>
         </is>
       </c>
       <c r="BE16" t="inlineStr">
         <is>
-          <t>0.1745</t>
+          <t>0.119</t>
         </is>
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>27.39</t>
-        </is>
-      </c>
-      <c r="BG16" t="inlineStr"/>
-      <c r="BH16" t="inlineStr"/>
+          <t>19.6</t>
+        </is>
+      </c>
+      <c r="BG16" t="inlineStr">
+        <is>
+          <t>L To R</t>
+        </is>
+      </c>
+      <c r="BH16" t="inlineStr">
+        <is>
+          <t>79</t>
+        </is>
+      </c>
       <c r="BI16" t="inlineStr">
         <is>
           <t>Truist Park</t>
@@ -10169,24 +10301,24 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>681082</t>
+          <t>645277</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Bryson Stott</t>
+          <t>Ozzie Albies</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
+          <t>ATL</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
           <t>PHI</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>ATL</t>
-        </is>
-      </c>
       <c r="F17" t="inlineStr">
         <is>
           <t>2026-10-02T00:00:00Z</t>
@@ -10194,31 +10326,31 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Ray Kerr</t>
+          <t>Aaron Nola</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>678061</t>
+          <t>605400</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L17" t="n">
-        <v>36.9</v>
+        <v>38.4</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
@@ -10232,65 +10364,61 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P17" t="n">
-        <v>25.2</v>
+        <v>15.3</v>
       </c>
       <c r="Q17" t="n">
-        <v>20</v>
+        <v>47.3</v>
       </c>
       <c r="R17" t="n">
-        <v>30.9</v>
+        <v>52.9</v>
       </c>
       <c r="S17" t="n">
-        <v>90.40000000000001</v>
+        <v>52.4</v>
       </c>
       <c r="T17" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="U17" t="n">
-        <v>40.7</v>
+        <v>0</v>
       </c>
       <c r="V17" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W17" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X17" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Y17" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr"/>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD17" t="inlineStr"/>
@@ -10307,12 +10435,12 @@
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
@@ -10322,12 +10450,12 @@
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>Contact streak: 9/23 over last 7 games</t>
+          <t>Last 7 games: 3/25, 0 HR</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 5.9% barrel, 2.0 HR allowed</t>
+          <t>switch hitter; pitcher baseline 9.2% barrel, 31.3 HR allowed</t>
         </is>
       </c>
       <c r="AM17" t="inlineStr">
@@ -10337,101 +10465,109 @@
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>5.66</t>
+          <t>4.13</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>35.24</t>
+          <t>28.6</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>88.86</t>
+          <t>87.22</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>98.4048</t>
+          <t>96.687</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>0.3993</t>
+          <t>0.346</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
         <is>
-          <t>0.1383</t>
+          <t>0.1184</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>0.3249</t>
+          <t>0.2808</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
         <is>
-          <t>69.72</t>
+          <t>68.86</t>
         </is>
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>6.75</t>
+          <t>5.67</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>34.17</t>
+          <t>46.7</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>27.59</t>
+          <t>31.48</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>10.9</t>
+          <t>20.2</t>
         </is>
       </c>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>0.1417</t>
+          <t>0.146</t>
         </is>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>5.9</t>
+          <t>9.24</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>31.4</t>
+          <t>41.2</t>
         </is>
       </c>
       <c r="BC17" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>88.77</t>
         </is>
       </c>
       <c r="BD17" t="inlineStr">
         <is>
-          <t>0.357</t>
+          <t>0.4184</t>
         </is>
       </c>
       <c r="BE17" t="inlineStr">
         <is>
-          <t>0.119</t>
+          <t>0.1745</t>
         </is>
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>19.6</t>
-        </is>
-      </c>
-      <c r="BG17" t="inlineStr"/>
-      <c r="BH17" t="inlineStr"/>
+          <t>27.39</t>
+        </is>
+      </c>
+      <c r="BG17" t="inlineStr">
+        <is>
+          <t>L To R</t>
+        </is>
+      </c>
+      <c r="BH17" t="inlineStr">
+        <is>
+          <t>79</t>
+        </is>
+      </c>
       <c r="BI17" t="inlineStr">
         <is>
           <t>Truist Park</t>
@@ -10470,12 +10606,12 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -10494,7 +10630,7 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>32.7</v>
+        <v>37.7</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
@@ -10508,7 +10644,7 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P18" t="n">
@@ -10518,10 +10654,10 @@
         <v>20</v>
       </c>
       <c r="R18" t="n">
-        <v>30.9</v>
+        <v>52.9</v>
       </c>
       <c r="S18" t="n">
-        <v>40.2</v>
+        <v>52.4</v>
       </c>
       <c r="T18" t="n">
         <v>78</v>
@@ -10531,39 +10667,35 @@
       </c>
       <c r="V18" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W18" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X18" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="Y18" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr"/>
       <c r="AC18" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026</t>
@@ -10706,8 +10838,16 @@
           <t>19.6</t>
         </is>
       </c>
-      <c r="BG18" t="inlineStr"/>
-      <c r="BH18" t="inlineStr"/>
+      <c r="BG18" t="inlineStr">
+        <is>
+          <t>L To R</t>
+        </is>
+      </c>
+      <c r="BH18" t="inlineStr">
+        <is>
+          <t>79</t>
+        </is>
+      </c>
       <c r="BI18" t="inlineStr">
         <is>
           <t>Truist Park</t>
@@ -10746,12 +10886,12 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -10770,7 +10910,7 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>25.1</v>
+        <v>28</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
@@ -10784,7 +10924,7 @@
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>No major boost</t>
         </is>
       </c>
       <c r="P19" t="n">
@@ -10794,10 +10934,10 @@
         <v>20</v>
       </c>
       <c r="R19" t="n">
-        <v>30.9</v>
+        <v>52.9</v>
       </c>
       <c r="S19" t="n">
-        <v>47.9</v>
+        <v>44.8</v>
       </c>
       <c r="T19" t="n">
         <v>50</v>
@@ -10807,39 +10947,35 @@
       </c>
       <c r="V19" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W19" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X19" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="Y19" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr"/>
       <c r="AC19" t="inlineStr">
         <is>
           <t>H:2026 P:2026</t>
@@ -10982,8 +11118,16 @@
           <t>19.6</t>
         </is>
       </c>
-      <c r="BG19" t="inlineStr"/>
-      <c r="BH19" t="inlineStr"/>
+      <c r="BG19" t="inlineStr">
+        <is>
+          <t>L To R</t>
+        </is>
+      </c>
+      <c r="BH19" t="inlineStr">
+        <is>
+          <t>79</t>
+        </is>
+      </c>
       <c r="BI19" t="inlineStr">
         <is>
           <t>Truist Park</t>

--- a/outputs/daily/hr_rankings_2026-10-01.xlsx
+++ b/outputs/daily/hr_rankings_2026-10-01.xlsx
@@ -760,7 +760,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -1320,7 +1320,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -1600,7 +1600,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1880,7 +1880,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -2160,7 +2160,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -2440,7 +2440,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -2720,7 +2720,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -3000,7 +3000,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -3280,7 +3280,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -3560,7 +3560,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -3840,7 +3840,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -4120,7 +4120,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -4400,7 +4400,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -4680,7 +4680,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -4960,7 +4960,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -5240,7 +5240,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -5520,7 +5520,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -6126,7 +6126,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -6406,7 +6406,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -6686,7 +6686,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -6966,7 +6966,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -7246,7 +7246,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -7526,7 +7526,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -7806,7 +7806,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -8086,7 +8086,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -8366,7 +8366,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -8646,7 +8646,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -8926,7 +8926,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -9206,7 +9206,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -9486,7 +9486,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -9766,7 +9766,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -10046,7 +10046,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -10326,7 +10326,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -10606,7 +10606,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -10886,7 +10886,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
